--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3427,154 +3427,154 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>レポート</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>不合格</v>
+        <v>コードポイント</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>件のチェック</v>
+        <v>ゲインカーブ</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>{lib} 採用</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>通知を受け取る</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>閉じる</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>メールアドレス</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>you@example.com</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>（任意）</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>キャンセル</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="397">
@@ -3582,23 +3582,23 @@
         <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>登録</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="400">
@@ -3611,535 +3611,631 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>エラー:</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>XML に変換</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>JSON に変換</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>ICC に変換</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>XML に変換中…</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>JSON に変換中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>ICC に変換中…</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>プロファイル ID</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>タグが見つかりません。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>タグ名</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>オフセット</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>サイズ</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>パディング</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>型</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>{type} の配列</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>（内容なし）</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>バイト</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>検証出力なし</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>プロファイルは有効です</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>重大な検証エラー</v>
+        <v>型</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>不明な検証ステータス</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>有効</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>警告</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>エラー</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>不明</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>合格</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>不合格</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>コンテキストで表示</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>検証の詳細</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>トリガー項目</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>項目</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>現在の値</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>必須: 0</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>期待値: {value}</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>無効</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>閉じる</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>インデント</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>キーをソート</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3451,791 +3451,951 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>原色</v>
+        <v>環境</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>伝達特性</v>
+        <v>検出中…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>マトリクス係数</v>
+        <v>環境を検出できませんでした。</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>HDR ディスプレイ</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>フルレンジ</v>
+        <v>広色域</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>ナローレンジ</v>
+        <v>HDR キャンバス経路</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>あり</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>レポート</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>不合格</v>
+        <v>報告なし</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>件のチェック</v>
+        <v>形式</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>検査</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>表示</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>{lib} 採用</v>
+        <v>埋め込み ICC プロファイルを読む — コーデック不要</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>通知を受け取る</v>
+        <v>ピクセルを表示</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>白より明るく描画</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool 自身がデコードするためブラウザに依存しません</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>閉じる</v>
+        <v>ブラウザはディスプレイの HDR ヘッドルーム量を報告できず、HDR 経路の有無のみ分かります。</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>メールアドレス</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>you@example.com</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>（任意）</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>キャンセル</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>登録</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>閉じる</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>エラー:</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>XML に変換</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>JSON に変換</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>ICC に変換</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>XML に変換中…</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>JSON に変換中…</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>ICC に変換中…</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>プロファイル ID</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>タグが見つかりません。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>タグ名</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>オフセット</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>サイズ</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>パディング</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>型</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>{type} の配列</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>（内容なし）</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>バイト</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>検証出力なし</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>プロファイルは有効です</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>不明な検証ステータス</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>有効</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>警告</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>エラー</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>不明</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>合格</v>
+        <v>型</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>不合格</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>コンテキストで表示</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>検証の詳細</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>トリガー項目</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>項目</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>現在の値</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>必須: 0</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>期待値: {value}</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>無効</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>閉じる</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>インデント</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>キーをソート</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3459,943 +3459,975 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>検出中…</v>
+        <v>SDR フォールバックを表示中</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>環境を検出できませんでした。</v>
+        <v>チェーンに HDR プロファイル</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR ディスプレイ</v>
+        <v>HDR プロファイルを通す変換はその AToB0Tag（8.10.6 が要求する焼き込み済み SDR レンダリング）を使います。8.10.1 が TRC タグを許さないためです。結果はそのフォールバックであり、HDR の挙動ではありません。</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>広色域</v>
+        <v>これらは TRC タグを持たない HDR プロファイルのため、色域は AToB0Tag から構築されます。これは HDR 処理を行わないコンシューマ向けに 8.10.6 が要求する焼き込み済み SDR レンダリングです。プロファイルの HDR 色域ではなく、それは有界の PCS には描けません。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>HDR キャンバス経路</v>
+        <v>検出中…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>環境を検出できませんでした。</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>なし</v>
+        <v>HDR ディスプレイ</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>あり</v>
+        <v>広色域</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>なし</v>
+        <v>HDR キャンバス経路</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>報告なし</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>形式</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>検査</v>
+        <v>あり</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>表示</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>報告なし</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>埋め込み ICC プロファイルを読む — コーデック不要</v>
+        <v>形式</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>ピクセルを表示</v>
+        <v>検査</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>白より明るく描画</v>
+        <v>表示</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>profiletool 自身がデコードするためブラウザに依存しません</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>ブラウザはディスプレイの HDR ヘッドルーム量を報告できず、HDR 経路の有無のみ分かります。</v>
+        <v>埋め込み ICC プロファイルを読む — コーデック不要</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>原色</v>
+        <v>ピクセルを表示</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>伝達特性</v>
+        <v>白より明るく描画</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>マトリクス係数</v>
+        <v>profiletool 自身がデコードするためブラウザに依存しません</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>ブラウザはディスプレイの HDR ヘッドルーム量を報告できず、HDR 経路の有無のみ分かります。</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>フルレンジ</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>ナローレンジ</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>レポート</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>不合格</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>件のチェック</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>{lib} 採用</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>通知を受け取る</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>閉じる</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>you@example.com</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>（任意）</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>キャンセル</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>登録</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>閉じる</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>エラー:</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>XML に変換</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>JSON に変換</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>ICC に変換</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>XML に変換中…</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>プロファイル ID</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>タグ名</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>オフセット</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>サイズ</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>パディング</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>型</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>{type} の配列</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>（内容なし）</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>バイト</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>型</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>検証出力なし</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>プロファイルは有効です</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>重大な検証エラー</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>不明な検証ステータス</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>有効</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>警告</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>エラー</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>不明</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>合格</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>不合格</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>コンテキストで表示</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>検証の詳細</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>トリガー項目</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>項目</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>現在の値</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>必須: 0</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>期待値: {value}</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>無効</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>閉じる</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>インデント</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>キーをソート</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3643,791 +3643,871 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>原色</v>
+        <v>ブラウザのフラグ</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>伝達特性</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>マトリクス係数</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>ここでは検出できません</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>フルレンジ</v>
+        <v>このブラウザで HDR を描画するのに必要です。WebGPU がないため、HDR キャンバスが唯一の経路です。プロファイルの検査はこれなしで動作します。</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>ナローレンジ</v>
+        <v>任意：HDR は WebGPU で描画できますが、有効にすると HDR キャンバス経路が加わり、profiletool が画面の実際の HDR ヘッドルームを読めるようになります。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>Web ページはフラグのページを開けません。これをアドレスバーに貼り付けて Enabled にし、ブラウザを再起動してください。</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>コピー</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>コピーしました</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>レポート</v>
+        <v>コピーに失敗しました — アドレスを選択してコピーしてください。</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>不合格</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>件のチェック</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>{lib} 採用</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>通知を受け取る</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>閉じる</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>メールアドレス</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>you@example.com</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>（任意）</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>キャンセル</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>登録</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>閉じる</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>エラー:</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>XML に変換</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>JSON に変換</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC に変換</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>XML に変換中…</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>JSON に変換中…</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>ICC に変換中…</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>プロファイル ID</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>タグが見つかりません。</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>タグ名</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>オフセット</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>サイズ</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>パディング</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>型</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>{type} の配列</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>（内容なし）</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>バイト</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>検証出力なし</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>プロファイルは有効です</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>型</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>重大な検証エラー</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>不明な検証ステータス</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>有効</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>警告</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>エラー</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>不明</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>合格</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>不合格</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>コンテキストで表示</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>検証の詳細</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>トリガー項目</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>項目</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>現在の値</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>必須: 0</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>期待値: {value}</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>無効</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>閉じる</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>インデント</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>キーをソート</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>ブラウザはディスプレイの HDR ヘッドルーム量を報告できず、HDR 経路の有無のみ分かります。</v>
+        <v>このブラウザはディスプレイの HDR ヘッドルームを報告しておらず、HDR 経路の有無のみ分かります。</v>
       </c>
     </row>
     <row r="405">
@@ -3723,791 +3723,927 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>原色</v>
+        <v>ピクセル比</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>伝達特性</v>
+        <v>現在のモニター</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>マトリクス係数</v>
+        <v>名前なし</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>メイン</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>フルレンジ</v>
+        <v>内蔵</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>ナローレンジ</v>
+        <v>HDR ヘッドルーム</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>このブラウザでは公開されていません</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ブラウザが報告した値をそのまま表示します。単位はまだ標準化されていません。SDR 画面では 0 が報告されました。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>レポート</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>不合格</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>件のチェック</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>{lib} 採用</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>通知を受け取る</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>閉じる</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>メールアドレス</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>you@example.com</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>（任意）</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>キャンセル</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>登録</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>閉じる</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>エラー:</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>XML に変換</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>JSON に変換</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>ICC に変換</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>XML に変換中…</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>JSON に変換中…</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>ICC に変換中…</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>プロファイル ID</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>タグが見つかりません。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>タグ名</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>オフセット</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>サイズ</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>パディング</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>型</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>{type} の配列</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>（内容なし）</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>バイト</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>検証出力なし</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>プロファイルは有効です</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>重大な検証エラー</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>不明な検証ステータス</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>有効</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>警告</v>
+        <v>型</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>エラー</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>不明</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>合格</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>不合格</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>コンテキストで表示</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>検証の詳細</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>トリガー項目</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>項目</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>現在の値</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>必須: 0</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>期待値: {value}</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>無効</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>閉じる</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>インデント</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>キーをソート</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3779,871 +3779,879 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>ブラウザが報告した値をそのまま表示します。単位はまだ標準化されていません。SDR 画面では 0 が報告されました。</v>
+        <v>Chromium はこれを段（stop）で報告します：ディスプレイのピーク輝度 ÷ SDR 白レベルの log₂。Windows では、Chrome がディスプレイを読み直したとき（ウィンドウを別の画面へ移動、または Chrome を再アクティブ化）にのみ更新され、明るさを変えても更新されません。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>{stops} 段（≈ SDR 白の {ratio} 倍）</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>ディスプレイを識別</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>ディスプレイイベント</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>原色</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>伝達特性</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>マトリクス係数</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>フルレンジ</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>ナローレンジ</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>レポート</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>you@example.com</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>（任意）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>登録</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>閉じる</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>エラー:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3795,863 +3795,1383 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>ディスプレイを識別</v>
+        <v>指定ディスプレイヘッドルームでのゲイン</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>このディスプレイで HDR 画像を 1 枚表示します。ブラウザがデコードできるファイルはブラウザ自身が表示し、OpenEXR は profiletool がデコードして描画します。</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>HDR 画像をここにドロップするか、クリックして選択</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>OpenEXR、AVIF、JPEG（ゲインマップ JPEG を含む）、PNG——Safari では HEIC も。</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>別の画像を選択</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>ディスプレイイベント</v>
+        <v>埋め込み ICC プロファイル</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>なし——OpenEXR は色度座標で色を表します</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>原色</v>
+        <v>確認中…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>伝達特性</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>マトリクス係数</v>
+        <v>プロファイルタブで開く</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>ゲインマップ</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>フルレンジ</v>
+        <v>検出、未デコード</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>ナローレンジ</v>
+        <v>画像ではありません。プロファイルはプロファイルパネルから読み込んでください。</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>profiletool が認識できない画像形式です。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>TIFF のピクセルはまだここに表示されません。ブラウザは TIFF をデコードせず、16 ビット TIFF での HDR の符号化方法も未定です（フェーズ 4.3）。埋め込みプロファイルは確認できます。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>この画像はここでは表示できません：</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>レポート</v>
+        <v>埋め込みプロファイルは確認できます。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>不合格</v>
+        <v>表示元</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>件のチェック</v>
+        <v>ブラウザ</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>HDR ディスプレイ</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>埋め込み ICC プロファイルだけで示された HDR はブラウザに無視されるため、この画像は暗く平坦に見える場合があります。</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>{lib} 採用</v>
+        <v>このブラウザは画像を SDR と HDR で切り替えられないため、ブラウザの描画のまま表示します。</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>通知を受け取る</v>
+        <v>ブラウザはこの画像をデコードできませんでした。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>HDR キャンバス（float16）</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>閉じる</v>
+        <v>WebGPU（拡張レンジ）</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>SDR キャンバス（トーンマップ）</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>メールアドレス</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>you@example.com</v>
+        <v>最も明るいピクセル</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>SDR 白の {n} 倍</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>（任意）</v>
+        <v>色度座標</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>記載なし——Rec. 709 と仮定</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>{from} はここでは使えません（{why}）。次の出力を使います。</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>キャンセル</v>
+        <v>この出力は白より明るい値を扱えないため、トーンマップした SDR 描画を表示します。</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>登録</v>
+        <v>露出</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>{n} 段</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>デコードできません：</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>閉じる</v>
+        <v>デコード中…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>ダイナミックレンジ</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>このブラウザは両端のみで、中間の混合はできません。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>エラー:</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>XML に変換</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>JSON に変換</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>ICC に変換</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>XML に変換中…</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>JSON に変換中…</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>ICC に変換中…</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>プロファイル ID</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>タグが見つかりません。</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>タグ名</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>オフセット</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>サイズ</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>パディング</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>型</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>{type} の配列</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>（内容なし）</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>バイト</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>検証出力なし</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>プロファイルは有効です</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>重大な検証エラー</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>不明な検証ステータス</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>有効</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>警告</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>エラー</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>不明</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>合格</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>不合格</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>コンテキストで表示</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>検証の詳細</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>トリガー項目</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>項目</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>現在の値</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>必須: 0</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>期待値: {value}</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>無効</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>閉じる</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>インデント</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>キーをソート</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>プライバシーに関する通知</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>有効なメールアドレスを入力してください。</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>フォームを確認してもう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>ネットワークエラーです。もう一度お試しください。</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>エラー:</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>XML に変換</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>JSON に変換</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>ICC に変換</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>XML に変換中…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>JSON に変換中…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>ICC に変換中…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>ICC プロファイルを読み込み</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>プロファイル ID</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>タグが見つかりません。</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>タグ名</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>オフセット</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>サイズ</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>パディング</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>読み込み後にバイトが変更されました</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>型</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>{type} の配列</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>（内容なし）</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>バイト</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>完全な説明を読み込み中…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>完全な説明を読み込めませんでした:</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>検証出力なし</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>プロファイルは有効です</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>プロファイルに警告があります</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>プロファイルは仕様に準拠していません</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>重大な検証エラー</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>不明な検証ステータス</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>重大 — 検査用にのみ表示</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>警告またはエラーは見つかりませんでした。</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>有効</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>エラー</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4139,1039 +4139,1175 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>profiletool 自身がデコードするため、ブラウザに依存しません</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>このブラウザはデコードできます</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>このブラウザはデコードできません</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>ベースライン</v>
+        <v>HEIC の表示には Safari などの WebKit ブラウザが必要です——Chrome と Firefox は macOS を含むどのプラットフォームでも HEIC をデコードしません</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>JPEG XL の表示には Safari が必要です。他のブラウザは未対応です</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>今後のリリースに延期</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>このディスプレイは HDR 経路を報告しないため、HDR はトーンマップした SDR で表示されます</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>このブラウザには HDR キャンバス経路がありません（float16 キャンバスか WebGPU が必要）</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>Firefox は HDR 画像を表示せず、ゲインマップも読みません。HDR コンテンツは SDR で表示されます</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>確認にはコンテナの解析だけが必要で、コーデックは不要です</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>HDR ディスプレイと HDR キャンバス経路の両方が使えます</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>不明な形式</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>{h} 段で適用</v>
+        <v>{os} 上の {browser}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>{name} · HDR ディスプレイを検出</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>{name} · SDR ディスプレイ</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>WebGPU がトーンマッピング「{mode}」を適用したため、出力は SDR に制限されます</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>このブラウザは適用した WebGPU トーンマッピングを報告しないため、HDR 出力は未確認です</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>変化なし</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>{h} 段での出力</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>ディスプレイを識別</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>ディスプレイイベント</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>原色</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>伝達特性</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>マトリクス係数</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>フルレンジ</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>ナローレンジ</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>レポート</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>不合格</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>件のチェック</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>{lib} 採用</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>通知を受け取る</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>閉じる</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>メールアドレス</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>you@example.com</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>（任意）</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>キャンセル</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>登録</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>閉じる</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>エラー:</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>XML に変換</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>JSON に変換</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>ICC に変換</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>XML に変換中…</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>JSON に変換中…</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>ICC に変換中…</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>プロファイル ID</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>タグが見つかりません。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>タグ名</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>オフセット</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>サイズ</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>パディング</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>型</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>{type} の配列</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>（内容なし）</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>バイト</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>検証出力なし</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>プロファイルは有効です</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>重大な検証エラー</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>不明な検証ステータス</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>有効</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>警告</v>
+        <v>型</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>エラー</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>不明</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>合格</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>不合格</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>コンテキストで表示</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>検証の詳細</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>トリガー項目</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>項目</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>現在の値</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>必須: 0</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>期待値: {value}</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>無効</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>閉じる</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>インデント</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>キーをソート</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4275,1039 +4275,1143 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>SDR 白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>1× — SDR ディスプレイ</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>ベースライン</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>このディスプレイは HDR を報告しないため、ブラウザはどちらの端でもこの画像を SDR で表示します。</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>このディスプレイは HDR を報告しないため、SDR 白より明るい部分はクリップされます。「ディスプレイに合わせる」はトーンマップした描画を表示します。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>この画像は SDR 白の {img} 倍を必要としますが、このディスプレイは {disp} 倍までしか表示できないため、明るい値はクリップされます。「ディスプレイに合わせる」はそれらをディスプレイのピークへなだらかに収めます。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>ディスプレイに合わせる</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>上限なし</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>上限 {n} 段（{r}×）</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>{h} 段で適用</v>
+        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>変化なし</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>{h} 段での出力</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>ディスプレイを識別</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>ディスプレイイベント</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>原色</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>伝達特性</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>マトリクス係数</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>フルレンジ</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>ナローレンジ</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>レポート</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>不合格</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>件のチェック</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>{lib} 採用</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>通知を受け取る</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>閉じる</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>メールアドレス</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>you@example.com</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>（任意）</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>キャンセル</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>登録</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>エラー:</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>XML に変換</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>JSON に変換</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>ICC に変換</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>XML に変換中…</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>JSON に変換中…</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>ICC に変換中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>プロファイル ID</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>タグが見つかりません。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>タグ名</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>オフセット</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>サイズ</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>パディング</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>型</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>{type} の配列</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>（内容なし）</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>バイト</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>検証出力なし</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>プロファイルは有効です</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>重大な検証エラー</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>不明な検証ステータス</v>
+        <v>型</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>有効</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>警告</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>エラー</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>不明</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>合格</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>不合格</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>コンテキストで表示</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>検証の詳細</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>トリガー項目</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>項目</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>現在の値</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>必須: 0</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>期待値: {value}</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>無効</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>閉じる</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>インデント</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>キーをソート</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4379,1039 +4379,1055 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>SDR 白パッチ</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>ベースライン</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>{h} 段で適用</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>変化なし</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>{h} 段での出力</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>ディスプレイを識別</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>ディスプレイイベント</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>原色</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>伝達特性</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>マトリクス係数</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>フルレンジ</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>ナローレンジ</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>レポート</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>不合格</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>件のチェック</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>通知を受け取る</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>閉じる</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>メールアドレス</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>you@example.com</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>（任意）</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>キャンセル</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>登録</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>閉じる</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>エラー:</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>XML に変換</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>JSON に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>ICC に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>XML に変換中…</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>JSON に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>ICC に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>タグ名</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>オフセット</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>サイズ</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>パディング</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>型</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>{type} の配列</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>（内容なし）</v>
+        <v>型</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>バイト</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>検証出力なし</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>プロファイルは有効です</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>不明な検証ステータス</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>有効</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>警告</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>エラー</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>不明</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>合格</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>不合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>コンテキストで表示</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>検証の詳細</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>トリガー項目</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>現在の値</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>必須: 0</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>期待値: {value}</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>無効</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>閉じる</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>キーをソート</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4395,1039 +4395,1223 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>プロファイルを割り当て</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>なし——ファイル自身の指定どおり</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>埋め込みプロファイル（{n} B）</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>ベースライン</v>
+        <v>プール内の HDR プロファイル</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>埋め込みプロファイル</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>カラーエンジンの経路</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>HDR 経路、ゲインカーブ適用</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>HDR 経路、ゲインカーブなし</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>焼き込み AToB0——HDR 経路ではありません</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>伝達関数</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>HDR 基準白</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>{h} 段で適用</v>
+        <v>目標ヘッドルーム</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>基準白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>トーンマッピング</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>自動（8.10.3 項の優先順位）</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>ゲインカーブ（HAGC）</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>焼き込み SDR フォールバック（AToB0）</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>オフ——改訂前の CMM と同じ</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>変化なし</v>
+        <v>プロファイルを適用中…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>OpenEXR はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>{h} 段での出力</v>
+        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>ディスプレイを識別</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>ディスプレイイベント</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>原色</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>伝達特性</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>マトリクス係数</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>フルレンジ</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>ナローレンジ</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>レポート</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>不合格</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>件のチェック</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>{lib} 採用</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>通知を受け取る</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>閉じる</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>メールアドレス</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>you@example.com</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>（任意）</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>キャンセル</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>登録</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>閉じる</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>エラー:</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>XML に変換</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>JSON に変換</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>ICC に変換</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>XML に変換中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>JSON に変換中…</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC に変換中…</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>プロファイル ID</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>タグが見つかりません。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>タグ名</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>オフセット</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>サイズ</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>パディング</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>型</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>{type} の配列</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>（内容なし）</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>バイト</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>検証出力なし</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>プロファイルは有効です</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>重大な検証エラー</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>不明な検証ステータス</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>有効</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>警告</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>エラー</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>不明</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>合格</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>不合格</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>コンテキストで表示</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>検証の詳細</v>
+        <v>型</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>トリガー項目</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>項目</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>現在の値</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>必須: 0</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>期待値: {value}</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>無効</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>閉じる</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>インデント</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>キーをソート</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4579,1039 +4579,1103 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>HDR プロファイル</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>リニア伝達関数</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>非リニア伝達関数（PQ、HLG）</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>ベースライン</v>
+        <v>HDR プロファイル — リニア伝達関数</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>OpenEXR はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>{h} 段で適用</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>変化なし</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>{h} 段での出力</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>ディスプレイを識別</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>ディスプレイイベント</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>原色</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>伝達特性</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>マトリクス係数</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>フルレンジ</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>ナローレンジ</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>レポート</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>不合格</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>件のチェック</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>{lib} 採用</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>通知を受け取る</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>閉じる</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>メールアドレス</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>you@example.com</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>（任意）</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>キャンセル</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>登録</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>閉じる</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>エラー:</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>XML に変換</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>JSON に変換</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>ICC に変換</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>XML に変換中…</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>JSON に変換中…</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>ICC に変換中…</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>プロファイル ID</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>タグが見つかりません。</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>タグ名</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>オフセット</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>サイズ</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>パディング</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>型</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>{type} の配列</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>（内容なし）</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>バイト</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>検証出力なし</v>
+        <v>型</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>プロファイルは有効です</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>重大な検証エラー</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>不明な検証ステータス</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>有効</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>警告</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>エラー</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>不明</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>合格</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>不合格</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>コンテキストで表示</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>検証の詳細</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>トリガー項目</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>項目</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>現在の値</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>必須: 0</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>期待値: {value}</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>無効</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>閉じる</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>インデント</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>キーをソート</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>このディスプレイで HDR 画像を 1 枚表示します。ブラウザがデコードできるファイルはブラウザ自身が表示し、OpenEXR は profiletool がデコードして描画します。</v>
+        <v>このディスプレイで HDR 画像を 1 枚表示します。ブラウザがデコードできるファイルはブラウザ自身が表示し、OpenEXR と Radiance HDR は profiletool がデコードして描画します。</v>
       </c>
     </row>
     <row r="427">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR、AVIF、JPEG（ゲインマップ JPEG を含む）、PNG——Safari では HEIC も。</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（ゲインマップ JPEG を含む）、PNG——Safari では HEIC も。</v>
       </c>
     </row>
     <row r="429">
@@ -3867,1815 +3867,1823 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>確認中…</v>
+        <v>なし——Radiance HDR は PRIMARIES ヘッダーで色を表します</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>なし</v>
+        <v>確認中…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>プロファイルタブで開く</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>ゲインマップ</v>
+        <v>プロファイルタブで開く</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>検出、未デコード</v>
+        <v>ゲインマップ</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>画像ではありません。プロファイルはプロファイルパネルから読み込んでください。</v>
+        <v>検出、未デコード</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>profiletool が認識できない画像形式です。</v>
+        <v>画像ではありません。プロファイルはプロファイルパネルから読み込んでください。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>TIFF のピクセルはまだここに表示されません。ブラウザは TIFF をデコードせず、16 ビット TIFF での HDR の符号化方法も未定です（フェーズ 4.3）。埋め込みプロファイルは確認できます。</v>
+        <v>profiletool が認識できない画像形式です。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>この画像はここでは表示できません：</v>
+        <v>TIFF のピクセルはまだここに表示されません。ブラウザは TIFF をデコードせず、16 ビット TIFF での HDR の符号化方法も未定です（フェーズ 4.3）。埋め込みプロファイルは確認できます。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>埋め込みプロファイルは確認できます。</v>
+        <v>この画像はここでは表示できません：</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>表示元</v>
+        <v>埋め込みプロファイルは確認できます。</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>ブラウザ</v>
+        <v>表示元</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>ブラウザ</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>HDR ディスプレイ</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>埋め込み ICC プロファイルだけで示された HDR はブラウザに無視されるため、この画像は暗く平坦に見える場合があります。</v>
+        <v>HDR ディスプレイ</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>このブラウザは画像を SDR と HDR で切り替えられないため、ブラウザの描画のまま表示します。</v>
+        <v>埋め込み ICC プロファイルだけで示された HDR はブラウザに無視されるため、この画像は暗く平坦に見える場合があります。</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>ブラウザはこの画像をデコードできませんでした。</v>
+        <v>このブラウザは画像を SDR と HDR で切り替えられないため、ブラウザの描画のまま表示します。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>出力</v>
+        <v>ブラウザはこの画像をデコードできませんでした。</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>HDR キャンバス（float16）</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU（拡張レンジ）</v>
+        <v>HDR キャンバス（float16）</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>SDR キャンバス（トーンマップ）</v>
+        <v>WebGPU（拡張レンジ）</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>サイズ</v>
+        <v>SDR キャンバス（トーンマップ）</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>最も明るいピクセル</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>SDR 白の {n} 倍</v>
+        <v>最も明るいピクセル</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>色度座標</v>
+        <v>SDR 白の {n} 倍</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>記載なし——Rec. 709 と仮定</v>
+        <v>色度座標</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from} はここでは使えません（{why}）。次の出力を使います。</v>
+        <v>記載なし——Rec. 709 と仮定</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>この出力は白より明るい値を扱えないため、トーンマップした SDR 描画を表示します。</v>
+        <v>{from} はここでは使えません（{why}）。次の出力を使います。</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>露出</v>
+        <v>この出力は白より明るい値を扱えないため、トーンマップした SDR 描画を表示します。</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} 段</v>
+        <v>露出</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>デコードできません：</v>
+        <v>{n} 段</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>デコード中…</v>
+        <v>デコードできません：</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>ダイナミックレンジ</v>
+        <v>デコード中…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>このブラウザは両端のみで、中間の混合はできません。</v>
+        <v>ダイナミックレンジ</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>profiletool 自身がデコードするため、ブラウザに依存しません</v>
+        <v>このブラウザは両端のみで、中間の混合はできません。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>このブラウザはデコードできます</v>
+        <v>profiletool 自身がデコードするため、ブラウザに依存しません</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>このブラウザはデコードできません</v>
+        <v>このブラウザはデコードできます</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>HEIC の表示には Safari などの WebKit ブラウザが必要です——Chrome と Firefox は macOS を含むどのプラットフォームでも HEIC をデコードしません</v>
+        <v>このブラウザはデコードできません</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>JPEG XL の表示には Safari が必要です。他のブラウザは未対応です</v>
+        <v>HEIC の表示には Safari などの WebKit ブラウザが必要です——Chrome と Firefox は macOS を含むどのプラットフォームでも HEIC をデコードしません</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>今後のリリースに延期</v>
+        <v>JPEG XL の表示には Safari が必要です。他のブラウザは未対応です</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>このディスプレイは HDR 経路を報告しないため、HDR はトーンマップした SDR で表示されます</v>
+        <v>今後のリリースに延期</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>このブラウザには HDR キャンバス経路がありません（float16 キャンバスか WebGPU が必要）</v>
+        <v>このディスプレイは HDR 経路を報告しないため、HDR はトーンマップした SDR で表示されます</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox は HDR 画像を表示せず、ゲインマップも読みません。HDR コンテンツは SDR で表示されます</v>
+        <v>このブラウザには HDR キャンバス経路がありません（float16 キャンバスか WebGPU が必要）</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>確認にはコンテナの解析だけが必要で、コーデックは不要です</v>
+        <v>Firefox は HDR 画像を表示せず、ゲインマップも読みません。HDR コンテンツは SDR で表示されます</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>HDR ディスプレイと HDR キャンバス経路の両方が使えます</v>
+        <v>確認にはコンテナの解析だけが必要で、コーデックは不要です</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>不明な形式</v>
+        <v>HDR ディスプレイと HDR キャンバス経路の両方が使えます</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{os} 上の {browser}</v>
+        <v>不明な形式</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · HDR ディスプレイを検出</v>
+        <v>{os} 上の {browser}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · SDR ディスプレイ</v>
+        <v>{name} · HDR ディスプレイを検出</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU がトーンマッピング「{mode}」を適用したため、出力は SDR に制限されます</v>
+        <v>{name} · SDR ディスプレイ</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>このブラウザは適用した WebGPU トーンマッピングを報告しないため、HDR 出力は未確認です</v>
+        <v>WebGPU がトーンマッピング「{mode}」を適用したため、出力は SDR に制限されます</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>ディスプレイのピーク</v>
+        <v>このブラウザは適用した WebGPU トーンマッピングを報告しないため、HDR 出力は未確認です</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>SDR 白の {r} 倍（{n} 段）</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× — SDR ディスプレイ</v>
+        <v>SDR 白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>不明</v>
+        <v>1× — SDR ディスプレイ</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>このディスプレイは HDR を報告しないため、ブラウザはどちらの端でもこの画像を SDR で表示します。</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>このディスプレイは HDR を報告しないため、SDR 白より明るい部分はクリップされます。「ディスプレイに合わせる」はトーンマップした描画を表示します。</v>
+        <v>このディスプレイは HDR を報告しないため、ブラウザはどちらの端でもこの画像を SDR で表示します。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>この画像は SDR 白の {img} 倍を必要としますが、このディスプレイは {disp} 倍までしか表示できないため、明るい値はクリップされます。「ディスプレイに合わせる」はそれらをディスプレイのピークへなだらかに収めます。</v>
+        <v>このディスプレイは HDR を報告しないため、SDR 白より明るい部分はクリップされます。「ディスプレイに合わせる」はトーンマップした描画を表示します。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>ディスプレイに合わせる</v>
+        <v>この画像は SDR 白の {img} 倍を必要としますが、このディスプレイは {disp} 倍までしか表示できないため、明るい値はクリップされます。「ディスプレイに合わせる」はそれらをディスプレイのピークへなだらかに収めます。</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
+        <v>ディスプレイに合わせる</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>上限なし</v>
+        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>上限 {n} 段（{r}×）</v>
+        <v>上限なし</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>SDR 白</v>
+        <v>上限 {n} 段（{r}×）</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>SDR 白パッチ</v>
+        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
+        <v>SDR 白パッチ</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>プロファイルを割り当て</v>
+        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>なし——ファイル自身の指定どおり</v>
+        <v>プロファイルを割り当て</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>埋め込みプロファイル（{n} B）</v>
+        <v>なし——ファイル自身の指定どおり</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>プール内の HDR プロファイル</v>
+        <v>埋め込みプロファイル（{n} B）</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>プロファイル</v>
+        <v>プール内の HDR プロファイル</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>埋め込みプロファイル</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>カラーエンジンの経路</v>
+        <v>埋め込みプロファイル</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR 経路、ゲインカーブ適用</v>
+        <v>カラーエンジンの経路</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR 経路、ゲインカーブなし</v>
+        <v>HDR 経路、ゲインカーブ適用</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>焼き込み AToB0——HDR 経路ではありません</v>
+        <v>HDR 経路、ゲインカーブなし</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>伝達関数</v>
+        <v>焼き込み AToB0——HDR 経路ではありません</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>HDR 基準白</v>
+        <v>伝達関数</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>目標ヘッドルーム</v>
+        <v>HDR 基準白</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>基準白の {r} 倍（{n} 段）</v>
+        <v>目標ヘッドルーム</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>トーンマッピング</v>
+        <v>基準白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>自動（8.10.3 項の優先順位）</v>
+        <v>トーンマッピング</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>ゲインカーブ（HAGC）</v>
+        <v>自動（8.10.3 項の優先順位）</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>焼き込み SDR フォールバック（AToB0）</v>
+        <v>ゲインカーブ（HAGC）</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>オフ——改訂前の CMM と同じ</v>
+        <v>焼き込み SDR フォールバック（AToB0）</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>プロファイルを適用中…</v>
+        <v>オフ——改訂前の CMM と同じ</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
+        <v>プロファイルを適用中…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
+        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
+        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR プロファイル</v>
+        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>リニア伝達関数</v>
+        <v>HDR プロファイル</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>非リニア伝達関数（PQ、HLG）</v>
+        <v>リニア伝達関数</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>HDR プロファイル — リニア伝達関数</v>
+        <v>非リニア伝達関数（PQ、HLG）</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
+        <v>HDR プロファイル — リニア伝達関数</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
+        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
+        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
+        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>ベースライン</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 段で適用</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>変化なし</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>{h} 段での出力</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>ディスプレイを識別</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>ディスプレイイベント</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>原色</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>伝達特性</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>マトリクス係数</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>フルレンジ</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>ナローレンジ</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>レポート</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>you@example.com</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>（任意）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>登録</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>閉じる</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>エラー:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4347,1343 +4347,1431 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
+        <v>画像の詳細</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>上限なし</v>
+        <v>使用不可——この画像はブラウザが描画するため、指定したピークに制限できません</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>上限 {n} 段（{r}×）</v>
+        <v>使用不可——この出力は SDR 白を超える明るさを表示できません</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>SDR 白</v>
+        <v>使用不可——このディスプレイのピークは不明です</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
+        <v>拡大</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>SDR 白パッチ</v>
+        <v>縮小</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
+        <v>画像を全体表示</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>プロファイルを割り当て</v>
+        <v>実ピクセル（1:1）</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>なし——ファイル自身の指定どおり</v>
+        <v>ドラッグでパン · Ctrl+ホイールでズーム · ダブルクリックでリセット</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>埋め込みプロファイル（{n} B）</v>
+        <v>ドラッグで画像領域のサイズを変更、ダブルクリックで既定サイズに戻します</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>プール内の HDR プロファイル</v>
+        <v>画像ビュー</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>プロファイル</v>
+        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>埋め込みプロファイル</v>
+        <v>上限なし</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>カラーエンジンの経路</v>
+        <v>上限 {n} 段（{r}×）</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR 経路、ゲインカーブ適用</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>HDR 経路、ゲインカーブなし</v>
+        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>焼き込み AToB0——HDR 経路ではありません</v>
+        <v>SDR 白パッチ</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>伝達関数</v>
+        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>HDR 基準白</v>
+        <v>プロファイルを割り当て</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>目標ヘッドルーム</v>
+        <v>なし——ファイル自身の指定どおり</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>基準白の {r} 倍（{n} 段）</v>
+        <v>埋め込みプロファイル（{n} B）</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>トーンマッピング</v>
+        <v>プール内の HDR プロファイル</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>自動（8.10.3 項の優先順位）</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>ゲインカーブ（HAGC）</v>
+        <v>埋め込みプロファイル</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>焼き込み SDR フォールバック（AToB0）</v>
+        <v>カラーエンジンの経路</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>オフ——改訂前の CMM と同じ</v>
+        <v>HDR 経路、ゲインカーブ適用</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>プロファイルを適用中…</v>
+        <v>HDR 経路、ゲインカーブなし</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
+        <v>焼き込み AToB0——HDR 経路ではありません</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
+        <v>伝達関数</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
+        <v>HDR 基準白</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR プロファイル</v>
+        <v>目標ヘッドルーム</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>リニア伝達関数</v>
+        <v>基準白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>非リニア伝達関数（PQ、HLG）</v>
+        <v>トーンマッピング</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR プロファイル — リニア伝達関数</v>
+        <v>自動（8.10.3 項の優先順位）</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
+        <v>ゲインカーブ（HAGC）</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
+        <v>焼き込み SDR フォールバック（AToB0）</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
+        <v>オフ——改訂前の CMM と同じ</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
+        <v>プロファイルを適用中…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>ベースライン</v>
+        <v>HDR プロファイル</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>リニア伝達関数</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>非リニア伝達関数（PQ、HLG）</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>HDR プロファイル — リニア伝達関数</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>{h} 段で適用</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>変化なし</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>{h} 段での出力</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>ディスプレイを識別</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>ディスプレイイベント</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>原色</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>伝達特性</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>マトリクス係数</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>フルレンジ</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>ナローレンジ</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>レポート</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>不合格</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>件のチェック</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>{lib} 採用</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>通知を受け取る</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>閉じる</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>メールアドレス</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>you@example.com</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>（任意）</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>キャンセル</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>登録</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>閉じる</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>エラー:</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>XML に変換</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>JSON に変換</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>ICC に変換</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>XML に変換中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>JSON に変換中…</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>ICC に変換中…</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>プロファイル ID</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>タグ名</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>オフセット</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>サイズ</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>パディング</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>型</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>{type} の配列</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>（内容なし）</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>バイト</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>検証出力なし</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>プロファイルは有効です</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>型</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>重大な検証エラー</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>不明な検証ステータス</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>有効</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>警告</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>エラー</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>不明</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>合格</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>不合格</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>コンテキストで表示</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>検証の詳細</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>トリガー項目</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>項目</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>現在の値</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>必須: 0</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>期待値: {value}</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>無効</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>閉じる</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>インデント</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>キーをソート</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4771,1007 +4771,1191 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>カラーエンジンによるプレビュー</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>{h} 段向けにトーンマッピング</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>基準白</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>プレビューを表示できません：{why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>{h} 段で適用</v>
+        <v>全ヘッドルームでのゲイン</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>入力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>ディスプレイのヘッドルーム（段）</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>ゲイン（段）</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>タグ内のカーブ</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>変化なし</v>
+        <v>スライダー</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>入力 = ディスプレイのピーク</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>{h} 段での出力</v>
+        <v>ヘッドルーム別のグレートーンカーブ</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>ディスプレイを識別</v>
+        <v>出力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>{h} 段</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>{h} 段（ベースライン）</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>{h} 段（スライダー）</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>ディスプレイイベント</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>原色</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>伝達特性</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>マトリクス係数</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>フルレンジ</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>ナローレンジ</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>レポート</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>不合格</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>件のチェック</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>{lib} 採用</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>通知を受け取る</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>閉じる</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>メールアドレス</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>you@example.com</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>（任意）</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>キャンセル</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>登録</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>閉じる</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>エラー:</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>XML に変換</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>JSON に変換</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>ICC に変換</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>XML に変換中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>JSON に変換中…</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>ICC に変換中…</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>プロファイル ID</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>タグが見つかりません。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>タグ名</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>オフセット</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>サイズ</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>パディング</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>型</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>{type} の配列</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>（内容なし）</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>バイト</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>検証出力なし</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>プロファイルは有効です</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>重大な検証エラー</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>不明な検証ステータス</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>有効</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>警告</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>エラー</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>不明</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>合格</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>不合格</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>コンテキストで表示</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>検証の詳細</v>
+        <v>型</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>トリガー項目</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>項目</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>現在の値</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>必須: 0</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>期待値: {value}</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>無効</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>閉じる</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>インデント</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>キーをソート</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>不明</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>合格</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>不合格</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>コンテキストで表示</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>検証の詳細</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>トリガー項目</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>項目</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>現在の値</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>必須: 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>期待値: {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>無効</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>閉じる</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>XML エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>JSON エディタを読み込み中…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4587,1375 +4587,1431 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>目標ヘッドルーム</v>
+        <v>リニア値</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>基準白の {r} 倍（{n} 段）</v>
+        <v>ファイルの 1.0 = HDR 基準白</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>トーンマッピング</v>
+        <v>ファイルの 1.0 = 1 cd/m²（ICC.1 箇条 8.10.2 a）</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>自動（8.10.3 項の優先順位）</v>
+        <v>OpenEXR と Radiance HDR のファイルは慣例として SDR 白を 1.0 に置きますが、ICC のリニア伝達関数は 1.0 を 1 cd/m² と解釈します。既定では、ファイルの 1.0 がプロファイルの HDR 基準白になるようにスケーリングします。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>ゲインカーブ（HAGC）</v>
+        <v>入力スケール</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>焼き込み SDR フォールバック（AToB0）</v>
+        <v>×{w} — ファイルの 1.0 = 基準白</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>オフ——改訂前の CMM と同じ</v>
+        <v>なし — ファイルの 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>プロファイルを適用中…</v>
+        <v>目標ヘッドルーム</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
+        <v>基準白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
+        <v>トーンマッピング</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
+        <v>自動（8.10.3 項の優先順位）</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>HDR プロファイル</v>
+        <v>ゲインカーブ（HAGC）</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>リニア伝達関数</v>
+        <v>焼き込み SDR フォールバック（AToB0）</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>非リニア伝達関数（PQ、HLG）</v>
+        <v>オフ——改訂前の CMM と同じ</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>HDR プロファイル — リニア伝達関数</v>
+        <v>プロファイルを適用中…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
+        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
+        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
+        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
+        <v>HDR プロファイル</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>リニア伝達関数</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>非リニア伝達関数（PQ、HLG）</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>HDR プロファイル — リニア伝達関数</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>ベースライン</v>
+        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>カラーエンジンによるプレビュー</v>
+        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
+        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>{h} 段向けにトーンマッピング</v>
+        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>基準白</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>ディスプレイのピーク</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>プレビューを表示できません：{why}</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
+        <v>カラーエンジンによるプレビュー</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>全ヘッドルームでのゲイン</v>
+        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
+        <v>{h} 段向けにトーンマッピング</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>入力（HDR 基準白に対する段数）</v>
+        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>ディスプレイのヘッドルーム（段）</v>
+        <v>基準白</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>ゲイン（段）</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>タグ内のカーブ</v>
+        <v>プレビューを表示できません：{why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>ベースライン</v>
+        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>スライダー</v>
+        <v>全ヘッドルームでのゲイン</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>入力 = ディスプレイのピーク</v>
+        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>ヘッドルーム別のグレートーンカーブ</v>
+        <v>入力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
+        <v>ディスプレイのヘッドルーム（段）</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>出力（HDR 基準白に対する段数）</v>
+        <v>ゲイン（段）</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} 段</v>
+        <v>タグ内のカーブ</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} 段（ベースライン）</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>{h} 段（スライダー）</v>
+        <v>スライダー</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>入力 = ディスプレイのピーク</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>ヘッドルーム別のグレートーンカーブ</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>出力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>{h} 段</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>{h} 段（ベースライン）</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>{h} 段（スライダー）</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>{h} 段で適用</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>変化なし</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>{h} 段での出力</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>ディスプレイを識別</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>ディスプレイイベント</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>原色</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>伝達特性</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>マトリクス係数</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>フルレンジ</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>ナローレンジ</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>レポート</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>不合格</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>件のチェック</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>{lib} 採用</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>通知を受け取る</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>閉じる</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>メールアドレス</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>you@example.com</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>（任意）</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>登録</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>閉じる</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>エラー:</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>XML に変換</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>JSON に変換</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>ICC に変換</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>XML に変換中…</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>JSON に変換中…</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>ICC に変換中…</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>プロファイル ID</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>タグが見つかりません。</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>タグ名</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>オフセット</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>サイズ</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>パディング</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>型</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>{type} の配列</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>（内容なし）</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>バイト</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>型</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>検証出力なし</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>プロファイルは有効です</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>重大な検証エラー</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>不明な検証ステータス</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>有効</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>警告</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>不明</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>合格</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>不合格</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>コンテキストで表示</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>検証の詳細</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>トリガー項目</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>項目</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>現在の値</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>必須: 0</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>期待値: {value}</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>無効</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>閉じる</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>インデント</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>キーをソート</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● 未保存の XML 編集</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -576,7 +576,7 @@
         <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>知覚参照媒体色域</v>
       </c>
     </row>
     <row r="23">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4123,1895 +4123,1935 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>デコード中…</v>
+        <v>このファイルは {size} MB です。HDR タブで開ける画像は {max} MB までです。</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>ダイナミックレンジ</v>
+        <v>プロファイルを適用できません：</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>このブラウザは両端のみで、中間の混合はできません。</v>
+        <v>画像を描画できません：</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>profiletool 自身がデコードするため、ブラウザに依存しません</v>
+        <v>（これらの原色は色空間を定義しません——無視し、Rec. 709 を使用）</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>このブラウザはデコードできます</v>
+        <v>JPEG XL のプロファイルはコードストリーム内で圧縮されており、profiletool はまだ展開できません</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>このブラウザはデコードできません</v>
+        <v>デコード中…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>HEIC の表示には Safari などの WebKit ブラウザが必要です——Chrome と Firefox は macOS を含むどのプラットフォームでも HEIC をデコードしません</v>
+        <v>ダイナミックレンジ</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>JPEG XL の表示には Safari が必要です。他のブラウザは未対応です</v>
+        <v>このブラウザは両端のみで、中間の混合はできません。</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>今後のリリースに延期</v>
+        <v>profiletool 自身がデコードするため、ブラウザに依存しません</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>このディスプレイは HDR 経路を報告しないため、HDR はトーンマップした SDR で表示されます</v>
+        <v>このブラウザはデコードできます</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>このブラウザには HDR キャンバス経路がありません（float16 キャンバスか WebGPU が必要）</v>
+        <v>このブラウザはデコードできません</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox は HDR 画像を表示せず、ゲインマップも読みません。HDR コンテンツは SDR で表示されます</v>
+        <v>HEIC の表示には Safari などの WebKit ブラウザが必要です——Chrome と Firefox は macOS を含むどのプラットフォームでも HEIC をデコードしません</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>確認にはコンテナの解析だけが必要で、コーデックは不要です</v>
+        <v>JPEG XL の表示には Safari が必要です。他のブラウザは未対応です</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>HDR ディスプレイと HDR キャンバス経路の両方が使えます</v>
+        <v>今後のリリースに延期</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>不明な形式</v>
+        <v>このディスプレイは HDR 経路を報告しないため、HDR はトーンマップした SDR で表示されます</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{os} 上の {browser}</v>
+        <v>このブラウザには HDR キャンバス経路がありません（float16 キャンバスか WebGPU が必要）</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · HDR ディスプレイを検出</v>
+        <v>Firefox は HDR 画像を表示せず、ゲインマップも読みません。HDR コンテンツは SDR で表示されます</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · SDR ディスプレイ</v>
+        <v>確認にはコンテナの解析だけが必要で、コーデックは不要です</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU がトーンマッピング「{mode}」を適用したため、出力は SDR に制限されます</v>
+        <v>HDR ディスプレイと HDR キャンバス経路の両方が使えます</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>このブラウザは適用した WebGPU トーンマッピングを報告しないため、HDR 出力は未確認です</v>
+        <v>不明な形式</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>ディスプレイのピーク</v>
+        <v>{os} 上の {browser}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>SDR 白の {r} 倍（{n} 段）</v>
+        <v>{name} · HDR ディスプレイを検出</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× — SDR ディスプレイ</v>
+        <v>{name} · SDR ディスプレイ</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>不明</v>
+        <v>WebGPU がトーンマッピング「{mode}」を適用したため、出力は SDR に制限されます</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>このディスプレイは HDR を報告しないため、ブラウザはどちらの端でもこの画像を SDR で表示します。</v>
+        <v>このブラウザは適用した WebGPU トーンマッピングを報告しないため、HDR 出力は未確認です</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>このディスプレイは HDR を報告しないため、SDR 白より明るい部分はクリップされます。「ディスプレイに合わせる」はトーンマップした描画を表示します。</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>この画像は SDR 白の {img} 倍を必要としますが、このディスプレイは {disp} 倍までしか表示できないため、明るい値はクリップされます。「ディスプレイに合わせる」はそれらをディスプレイのピークへなだらかに収めます。</v>
+        <v>SDR 白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>ディスプレイに合わせる</v>
+        <v>1× — SDR ディスプレイ</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>画像の詳細</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>使用不可——この画像はブラウザが描画するため、指定したピークに制限できません</v>
+        <v>このディスプレイは HDR を報告しないため、ブラウザはどちらの端でもこの画像を SDR で表示します。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>使用不可——この出力は SDR 白を超える明るさを表示できません</v>
+        <v>このディスプレイは HDR を報告しないため、SDR 白より明るい部分はクリップされます。「ディスプレイに合わせる」はトーンマップした描画を表示します。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>使用不可——このディスプレイのピークは不明です</v>
+        <v>この画像は SDR 白の {img} 倍を必要としますが、このディスプレイは {disp} 倍までしか表示できないため、明るい値はクリップされます。「ディスプレイに合わせる」はそれらをディスプレイのピークへなだらかに収めます。</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>拡大</v>
+        <v>ディスプレイに合わせる</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>縮小</v>
+        <v>画像の詳細</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>画像を全体表示</v>
+        <v>使用不可——この画像はブラウザが描画するため、指定したピークに制限できません</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>実ピクセル（1:1）</v>
+        <v>使用不可——この出力は SDR 白を超える明るさを表示できません</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>ドラッグでパン · Ctrl+ホイールでズーム · ダブルクリックでリセット</v>
+        <v>使用不可——このディスプレイのピークは不明です</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>ドラッグで画像領域のサイズを変更、ダブルクリックで既定サイズに戻します</v>
+        <v>拡大</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>画像ビュー</v>
+        <v>縮小</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
+        <v>画像を全体表示</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>上限なし</v>
+        <v>実ピクセル（1:1）</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>上限 {n} 段（{r}×）</v>
+        <v>ドラッグでパン · Ctrl+ホイールでズーム · ダブルクリックでリセット</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>SDR 白</v>
+        <v>ドラッグで画像領域のサイズを変更、ダブルクリックで既定サイズに戻します</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
+        <v>画像ビュー</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>SDR 白パッチ</v>
+        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
+        <v>上限なし</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>プロファイルを割り当て</v>
+        <v>上限 {n} 段（{r}×）</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>なし——ファイル自身の指定どおり</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>埋め込みプロファイル（{n} B）</v>
+        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>プール内の HDR プロファイル</v>
+        <v>SDR 白パッチ</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>プロファイル</v>
+        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>埋め込みプロファイル</v>
+        <v>プロファイルを割り当て</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>カラーエンジンの経路</v>
+        <v>なし——ファイル自身の指定どおり</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>HDR 経路、ゲインカーブ適用</v>
+        <v>埋め込みプロファイル（{n} B）</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR 経路、ゲインカーブなし</v>
+        <v>プール内の HDR プロファイル</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>焼き込み AToB0——HDR 経路ではありません</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>伝達関数</v>
+        <v>埋め込みプロファイル</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR 基準白</v>
+        <v>カラーエンジンの経路</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>リニア値</v>
+        <v>HDR 経路、ゲインカーブ適用</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>ファイルの 1.0 = HDR 基準白</v>
+        <v>HDR 経路、ゲインカーブなし</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>ファイルの 1.0 = 1 cd/m²（ICC.1 箇条 8.10.2 a）</v>
+        <v>焼き込み AToB0——HDR 経路ではありません</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>OpenEXR と Radiance HDR のファイルは慣例として SDR 白を 1.0 に置きますが、ICC のリニア伝達関数は 1.0 を 1 cd/m² と解釈します。既定では、ファイルの 1.0 がプロファイルの HDR 基準白になるようにスケーリングします。</v>
+        <v>伝達関数</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>入力スケール</v>
+        <v>HDR 基準白</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} — ファイルの 1.0 = 基準白</v>
+        <v>リニア値</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>なし — ファイルの 1.0 = 1 cd/m²</v>
+        <v>ファイルの 1.0 = HDR 基準白</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>目標ヘッドルーム</v>
+        <v>ファイルの 1.0 = 1 cd/m²（ICC.1 箇条 8.10.2 a）</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>基準白の {r} 倍（{n} 段）</v>
+        <v>OpenEXR と Radiance HDR のファイルは慣例として SDR 白を 1.0 に置きますが、ICC のリニア伝達関数は 1.0 を 1 cd/m² と解釈します。既定では、ファイルの 1.0 がプロファイルの HDR 基準白になるようにスケーリングします。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>トーンマッピング</v>
+        <v>入力スケール</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>自動（8.10.3 項の優先順位）</v>
+        <v>×{w} — ファイルの 1.0 = 基準白</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>ゲインカーブ（HAGC）</v>
+        <v>なし — ファイルの 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>焼き込み SDR フォールバック（AToB0）</v>
+        <v>目標ヘッドルーム</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>オフ——改訂前の CMM と同じ</v>
+        <v>基準白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>プロファイルを適用中…</v>
+        <v>トーンマッピング</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
+        <v>自動（8.10.3 項の優先順位）</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
+        <v>ゲインカーブ（HAGC）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
+        <v>焼き込み SDR フォールバック（AToB0）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>HDR プロファイル</v>
+        <v>オフ——改訂前の CMM と同じ</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>リニア伝達関数</v>
+        <v>プロファイルを適用中…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>非リニア伝達関数（PQ、HLG）</v>
+        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR プロファイル — リニア伝達関数</v>
+        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
+        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
+        <v>HDR プロファイル</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
+        <v>リニア伝達関数</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
+        <v>非リニア伝達関数（PQ、HLG）</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>HDR プロファイル — リニア伝達関数</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>ベースライン</v>
+        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>カラーエンジンによるプレビュー</v>
+        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>{h} 段向けにトーンマッピング</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>基準白</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>ディスプレイのピーク</v>
+        <v>カラーエンジンによるプレビュー</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>プレビューを表示できません：{why}</v>
+        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
+        <v>{h} 段向けにトーンマッピング</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>全ヘッドルームでのゲイン</v>
+        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
+        <v>基準白</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>入力（HDR 基準白に対する段数）</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>ディスプレイのヘッドルーム（段）</v>
+        <v>プレビューを表示できません：{why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>ゲイン（段）</v>
+        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>タグ内のカーブ</v>
+        <v>全ヘッドルームでのゲイン</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>ベースライン</v>
+        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>スライダー</v>
+        <v>入力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>入力 = ディスプレイのピーク</v>
+        <v>ディスプレイのヘッドルーム（段）</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>ヘッドルーム別のグレートーンカーブ</v>
+        <v>ゲイン（段）</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
+        <v>タグ内のカーブ</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>出力（HDR 基準白に対する段数）</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} 段</v>
+        <v>スライダー</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} 段（ベースライン）</v>
+        <v>入力 = ディスプレイのピーク</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>{h} 段（スライダー）</v>
+        <v>ヘッドルーム別のグレートーンカーブ</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>出力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>{h} 段</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>{h} 段（ベースライン）</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>{h} 段（スライダー）</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>{h} 段で適用</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>変化なし</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>{h} 段での出力</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>ディスプレイを識別</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>ディスプレイイベント</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>原色</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>伝達特性</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>マトリクス係数</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>フルレンジ</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>ナローレンジ</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>レポート</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>不合格</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>件のチェック</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>{lib} 採用</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>通知を受け取る</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>閉じる</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>メールアドレス</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>you@example.com</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>（任意）</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>キャンセル</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>登録</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>閉じる</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>エラー:</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>XML に変換</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>JSON に変換</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>ICC に変換</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>XML に変換中…</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>JSON に変換中…</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>ICC に変換中…</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>プロファイル ID</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>タグが見つかりません。</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>タグ名</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>オフセット</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>サイズ</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>パディング</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>型</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>{type} の配列</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>（内容なし）</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>バイト</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>型</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>検証出力なし</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>プロファイルは有効です</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>重大な検証エラー</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>不明な検証ステータス</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>有効</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>警告</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>エラー</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>不明</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>合格</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>不合格</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>コンテキストで表示</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>検証の詳細</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>トリガー項目</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>項目</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>現在の値</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>必須: 0</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>期待値: {value}</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>無効</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>閉じる</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>インデント</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>キーをソート</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● 未保存の JSON 編集</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>インデント</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（ゲインマップ JPEG を含む）、PNG——Safari では HEIC も。</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（ゲインマップ JPEG を含む）、PNG——Safari では HEIC と JPEG XL も。</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加され、ダウンロードされます。</v>
+        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加されて開かれます。「ICC プロファイルを保存」をクリックするまでダウンロードはされません。</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,4861 +1197,4869 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>名前で並べ替え</v>
+        <v>タップして選択し、タブをタップして送ります。</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>名前で並べ替え</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>.cube から新しいプロファイル</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加されて開かれます。「ICC プロファイルを保存」をクリックするまでダウンロードはされません。</v>
+        <v>.cube から新しいプロファイル</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>.cube ファイルを選択</v>
+        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加されて開かれます。「ICC プロファイルを保存」をクリックするまでダウンロードはされません。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>.cube ファイルを選択</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>またはここにドロップするか、下に貼り付けてください</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>キャンセル</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>DeviceLink を作成</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>作成中…</v>
+        <v>DeviceLink を作成</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>プロファイル</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>比較</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>リンク</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>スペクトル</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>プールからこのタブにプロファイルをドラッグします</v>
+        <v>スペクトル</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>削除</v>
+        <v>プールからこのタブにプロファイルをドラッグします</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>プロファイルが選択されていません</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
+        <v>プロファイルが選択されていません</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>まだ比較するものがありません</v>
+        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
+        <v>まだ比較するものがありません</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>色域比較</v>
+        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>レンダリングインテント</v>
+        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>シェル</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>ワイヤーフレーム</v>
+        <v>シェル</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>軸の数値</v>
+        <v>ワイヤーフレーム</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>不透明度</v>
+        <v>軸の数値</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>色</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>単色</v>
+        <v>色</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>値による</v>
+        <v>単色</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>色相による</v>
+        <v>値による</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>回転</v>
+        <v>色相による</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>ターンテーブル</v>
+        <v>回転</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>オービット</v>
+        <v>ターンテーブル</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>ドラッグ速度</v>
+        <v>オービット</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>ロール</v>
+        <v>ドラッグ速度</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>ロール速度</v>
+        <v>ロール</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>色域を構築中…</v>
+        <v>ロール速度</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>色域なし</v>
+        <v>色域を構築中…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>表示/非表示</v>
+        <v>色域なし</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D 色域シェル</v>
+        <v>表示/非表示</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D 色域スライス</v>
+        <v>3D 色域シェル</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>平面</v>
+        <v>2D 色域スライス</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>リンク</v>
+        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
+        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4 ディスプレイメーカー</v>
+        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
+        <v>V4 ディスプレイメーカー</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB ディスプレイ</v>
+        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>ディスプレイプロファイルをドロップ</v>
+        <v>V5 RGB ディスプレイ</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 オブザーバー (PCC)</v>
+        <v>ディスプレイプロファイルをドロップ</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>オブザーバープロファイルをドロップ</v>
+        <v>V5 オブザーバー (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
+        <v>オブザーバープロファイルをドロップ</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>V4 ディスプレイプロファイルを作成</v>
+        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>プロファイル名</v>
+        <v>V4 ディスプレイプロファイルを作成</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>作成</v>
+        <v>プロファイル名</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>作成中…</v>
+        <v>作成</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>リンクパイプライン</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
+        <v>リンクパイプライン</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>完了</v>
+        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
+        <v>完了</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>画像を確認中…</v>
+        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
+        <v>画像を確認中…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
+        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>画像を変換</v>
+        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>変換中…</v>
+        <v>画像を変換</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>削除済み</v>
+        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>前に移動</v>
+        <v>削除済み</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>後に移動</v>
+        <v>前に移動</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>上に移動</v>
+        <v>後に移動</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>下に移動</v>
+        <v>上に移動</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>レンダリングインテント（すべて）</v>
+        <v>下に移動</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>この変換のレンダリングインテント</v>
+        <v>レンダリングインテント（すべて）</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
+        <v>この変換のレンダリングインテント</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
+        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
+        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>チェーン</v>
+        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>チェーンを解析できませんでした。</v>
+        <v>チェーン</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>チェーンを確認中…</v>
+        <v>チェーンを解析できませんでした。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>チェーンが接続していません（{detail}）。</v>
+        <v>チェーンを確認中…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
+        <v>チェーンが接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>画像を処理する前にチェーンを修正してください</v>
+        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>クリア</v>
+        <v>画像を処理する前にチェーンを修正してください</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>DeviceLinkを作成</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink名</v>
+        <v>DeviceLinkを作成</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>作成中…</v>
+        <v>DeviceLink名</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>画像を処理するにはチェーンを作成してください</v>
+        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
+        <v>画像を処理するにはチェーンを作成してください</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>変換した画像を保存しました。</v>
+        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
+        <v>変換した画像を保存しました。</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>データファイルが大きすぎます。</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>データを変換</v>
+        <v>データファイルが大きすぎます。</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>変換中…</v>
+        <v>データを変換</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>優先</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>観測者</v>
+        <v>優先</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>光源</v>
+        <v>観測者</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>条件</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>重複を{n}件フィルタ</v>
+        <v>条件</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>中央値</v>
+        <v>重複を{n}件フィルタ</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>平均値</v>
+        <v>中央値</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>パッチ</v>
+        <v>平均値</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>重複{n}件</v>
+        <v>パッチ</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>変換結果</v>
+        <v>重複{n}件</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} ・ {n}パッチ</v>
+        <v>変換結果</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
+        <v>{src} → {dst} ・ {n}パッチ</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>名前を付けて保存</v>
+        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>保存</v>
+        <v>名前を付けて保存</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>変換を反転</v>
+        <v>保存</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>反転中…</v>
+        <v>変換を反転</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>反転</v>
+        <v>反転中…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>最後の段階</v>
+        <v>反転</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>最初の段階</v>
+        <v>最後の段階</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>{in}のデータ → {out}を検索</v>
+        <v>最初の段階</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
+        <v>{in}のデータ → {out}を検索</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
+        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔEコスト</v>
+        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>この画像には埋め込みICCプロファイルがあります。</v>
+        <v>ΔEコスト</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>抽出してチェーンに追加</v>
+        <v>この画像には埋め込みICCプロファイルがあります。</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>抽出中…</v>
+        <v>抽出してチェーンに追加</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>閉じる</v>
+        <v>抽出中…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>画像出力オプション</v>
+        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>エンコーディング</v>
+        <v>画像出力オプション</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>元と同じ</v>
+        <v>エンコーディング</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8ビット</v>
+        <v>元と同じ</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16ビット</v>
+        <v>8ビット</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>浮動小数点（32ビット）</v>
+        <v>16ビット</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>圧縮</v>
+        <v>浮動小数点（32ビット）</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>なし</v>
+        <v>圧縮</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>プレーナー</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>コンポジット</v>
+        <v>プレーナー</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>セパレート</v>
+        <v>コンポジット</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM補間</v>
+        <v>セパレート</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>四面体</v>
+        <v>CMM補間</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>線形</v>
+        <v>四面体</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>ICCを埋め込む</v>
+        <v>線形</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
+        <v>ICCを埋め込む</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>スペクトルTIFFを組み立て</v>
+        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
+        <v>スペクトルTIFFを組み立て</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
+        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>ch</v>
+        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>組み立てて保存</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>組み立て中…</v>
+        <v>組み立てて保存</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n}チャンネルを組み立てました。</v>
+        <v>組み立て中…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
+        <v>{n}チャンネルを組み立てました。</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>キャンセル</v>
+        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} 件のファイルが読み込まれませんでした</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
+        <v>{n} 件のファイルが読み込まれませんでした</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>または</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>ファイルを選択</v>
+        <v>または</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>ヘッダー</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>タグ</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>検証</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>分析</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>中立軸インキング</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>レンダリングインテント</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% インキ</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* 出力（トーン）</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 出力（トーン）</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>極値の測色</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>プロファイルの再現範囲の両端：基材の白、印刷できる最も暗い黒、その黒に要するインキ量、そして各色相が最も鮮やかになる点。</v>
+        <v>極値の測色</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>白色点は色材ゼロのときの色——すなわち素の基材です。黒色点は、PCS の黒（L*=0、a*=b*=0）を選択した B2A テーブルに通してプロファイルが黒に対して選ぶインキングを求め、そのインキングを A2B1 で読み戻して得られます。総インキ量（TAC）はそのインキングの合計です。絶対測色は基材そのものの色を示し、相対測色はそれを完全な白に基準化し直します。</v>
+        <v>プロファイルの再現範囲の両端：基材の白、印刷できる最も暗い黒、その黒に要するインキ量、そして各色相が最も鮮やかになる点。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>相対</v>
+        <v>白色点は色材ゼロのときの色——すなわち素の基材です。黒色点は、PCS の黒（L*=0、a*=b*=0）を選択した B2A テーブルに通してプロファイルが黒に対して選ぶインキングを求め、そのインキングを A2B1 で読み戻して得られます。総インキ量（TAC）はそのインキングの合計です。絶対測色は基材そのものの色を示し、相対測色はそれを完全な白に基準化し直します。</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>絶対</v>
+        <v>相対</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>白色点</v>
+        <v>絶対</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>黒色点</v>
+        <v>白色点</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>黒色点でのインキング</v>
+        <v>黒色点</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>黒色点でのインキング</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>このプロファイルにはメディア白色点タグがないため、絶対測色は利用できません。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>極値の測色は出力（プリンター）プロファイルでのみ利用できます——色材ゼロが素の基材であることを前提とします。</v>
+        <v>このプロファイルにはメディア白色点タグがないため、絶対測色は利用できません。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>ベタとクロマ最大点</v>
+        <v>極値の測色は出力（プリンター）プロファイルでのみ利用できます——色材ゼロが素の基材であることを前提とします。</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>各インキ頂点の位置と、そこに至る途中で最もクロマが高くなる点です。A2B1 を通して測るため、これらの行は上のレンダリングインテントでは変化しません。素性のよいプロファイルでは 2 つの行が一致します。クロマ最大点がベタより手前に来る場合、その先のインキは暗くしているだけです。</v>
+        <v>ベタとクロマ最大点</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>色相</v>
+        <v>各インキ頂点の位置と、そこに至る途中で最もクロマが高くなる点です。A2B1 を通して測るため、これらの行は上のレンダリングインテントでは変化しません。素性のよいプロファイルでは 2 つの行が一致します。クロマ最大点がベタより手前に来る場合、その先のインキは暗くしているだけです。</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>ベタ</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* 最大</v>
+        <v>ベタ</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>そのインキング</v>
+        <v>C* 最大</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>クロマ最大点がベタより手前で到達しています——この点より先のインキは暗くするだけです。</v>
+        <v>そのインキング</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>シャドウ部のインキ使用量</v>
+        <v>クロマ最大点がベタより手前で到達しています——この点より先のインキは暗くするだけです。</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>意図的に暗い一定の明度で a*b* 平面を横切る 4 本の直線経路を、選択した B2A テーブルに通します。すべてのサンプルが同じ L* を共有するため、ある色材に現れる急な段差や反転は色相とクロマの扱いのみに由来します——シャドウ部の色域マッピングアーティファクトの兆候です。</v>
+        <v>シャドウ部のインキ使用量</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>シャドウ部のインキ使用量は出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>意図的に暗い一定の明度で a*b* 平面を横切る 4 本の直線経路を、選択した B2A テーブルに通します。すべてのサンプルが同じ L* を共有するため、ある色材に現れる急な段差や反転は色相とクロマの扱いのみに由来します——シャドウ部の色域マッピングアーティファクトの兆候です。</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>L* 一定の平面</v>
+        <v>シャドウ部のインキ使用量は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>黒色点補償の起点</v>
+        <v>L* 一定の平面</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>経路上の位置</v>
+        <v>黒色点補償の起点</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>経路</v>
+        <v>経路上の位置</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>中性軸を通る一次色インキ経路</v>
+        <v>経路</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>色域内の3本の経路——シアン→レッド、マゼンタ→グリーン、イエロー→ブルー——それぞれが両端の明度の中点で中性軸を通り、選択した B2A テーブルを通ります。すべてのサンプルが色域内にあるため、シャドウ経路とは異なり、ある色材の急な段差や反転は色域マッピングのアーティファクトではなく CLUT の滑らかさの欠陥を示します。</v>
+        <v>中性軸を通る一次色インキ経路</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>一次色インキ経路は出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>色域内の3本の経路——シアン→レッド、マゼンタ→グリーン、イエロー→ブルー——それぞれが両端の明度の中点で中性軸を通り、選択した B2A テーブルを通ります。すべてのサンプルが色域内にあるため、シャドウ経路とは異なり、ある色材の急な段差や反転は色域マッピングのアーティファクトではなく CLUT の滑らかさの欠陥を示します。</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>経路上の位置（中点が中性）</v>
+        <v>一次色インキ経路は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>このインテントに黒点補償を適用しました。</v>
+        <v>経路上の位置（中点が中性）</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>インキ使用量の統計</v>
+        <v>このインテントに黒点補償を適用しました。</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>プロファイルが各色材をどれだけ使用するかを、合計と全体に対する割合で示します——分版のインキ消費の特徴です。</v>
+        <v>インキ使用量の統計</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>インキ使用量の統計は出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>プロファイルが各色材をどれだけ使用するかを、合計と全体に対する割合で示します——分版のインキ消費の特徴です。</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>中性軸</v>
+        <v>インキ使用量の統計は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>平均被覆率</v>
+        <v>中性軸</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>インキの割合</v>
+        <v>平均被覆率</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>インキの割合は中性構築の指紋です——各色材が使用インキ総量に占める割合で、サンプル数に依存しません。</v>
+        <v>インキの割合</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>色域内の点</v>
+        <v>インキの割合は中性構築の指紋です——各色材が使用インキ総量に占める割合で、サンプル数に依存しません。</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>色域内のすべての色に対するインキ使用量には B2A 方向の色域境界が必要ですが、まだ構築されていません——保留中です。</v>
+        <v>色域内の点</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>要約する色材データがありません。</v>
+        <v>色域内のすべての色に対するインキ使用量には B2A 方向の色域境界が必要ですが、まだ構築されていません——保留中です。</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>下で B2A（PCS→デバイス）テーブルを選択すると、各色材のグレースケールのインキ被覆画像も表示されます。</v>
+        <v>要約する色材データがありません。</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>同じ格子上での各色材のインキ被覆（暗いほどインキが多い）。</v>
+        <v>下で B2A（PCS→デバイス）テーブルを選択すると、各色材のグレースケールのインキ被覆画像も表示されます。</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>シアン</v>
+        <v>同じ格子上での各色材のインキ被覆（暗いほどインキが多い）。</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>マゼンタ</v>
+        <v>シアン</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>イエロー</v>
+        <v>マゼンタ</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>レッド</v>
+        <v>イエロー</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>グリーン</v>
+        <v>レッド</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>ブルー</v>
+        <v>グリーン</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>ブラック</v>
+        <v>ブルー</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>知覚的</v>
+        <v>ブラック</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>相対比色</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>彩度</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>絶対比色</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>プロファイル統計</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>レンダリングインテント</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>往復 ΔE</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>平均</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>分析中…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>分析</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>プロット</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>生出力</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>カーブ</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>入力カーブ</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>出力カーブ</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT 画像</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>色域画像</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>色度</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>散布図</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>カーブ表</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>テーブル</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>データ</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>評価</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>読み込み中…</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>入力</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>出力</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>浮動小数点</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>グリッド点</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>正規化</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>人間可読</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>デバイス → PCS</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → デバイス</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>読み込み中…</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>セキュリティ</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>適合性</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>品質</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>コードポイント</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>ゲインカーブ</v>
+        <v>コードポイント</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>環境</v>
+        <v>ゲインカーブ</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>SDR フォールバックを表示中</v>
+        <v>環境</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>チェーンに HDR プロファイル</v>
+        <v>SDR フォールバックを表示中</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR プロファイルを通す変換はその AToB0Tag（8.10.6 が要求する焼き込み済み SDR レンダリング）を使います。8.10.1 が TRC タグを許さないためです。結果はそのフォールバックであり、HDR の挙動ではありません。</v>
+        <v>チェーンに HDR プロファイル</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>これらは TRC タグを持たない HDR プロファイルのため、色域は AToB0Tag から構築されます。これは HDR 処理を行わないコンシューマ向けに 8.10.6 が要求する焼き込み済み SDR レンダリングです。プロファイルの HDR 色域ではなく、それは有界の PCS には描けません。</v>
+        <v>HDR プロファイルを通す変換はその AToB0Tag（8.10.6 が要求する焼き込み済み SDR レンダリング）を使います。8.10.1 が TRC タグを許さないためです。結果はそのフォールバックであり、HDR の挙動ではありません。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>検出中…</v>
+        <v>これらは TRC タグを持たない HDR プロファイルのため、色域は AToB0Tag から構築されます。これは HDR 処理を行わないコンシューマ向けに 8.10.6 が要求する焼き込み済み SDR レンダリングです。プロファイルの HDR 色域ではなく、それは有界の PCS には描けません。</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>環境を検出できませんでした。</v>
+        <v>検出中…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>HDR ディスプレイ</v>
+        <v>環境を検出できませんでした。</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>広色域</v>
+        <v>HDR ディスプレイ</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>HDR キャンバス経路</v>
+        <v>広色域</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>HDR キャンバス経路</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>なし</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>あり</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>なし</v>
+        <v>あり</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>報告なし</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>形式</v>
+        <v>報告なし</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>検査</v>
+        <v>形式</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>表示</v>
+        <v>検査</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>表示</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>埋め込み ICC プロファイルを読む — コーデック不要</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>ピクセルを表示</v>
+        <v>埋め込み ICC プロファイルを読む — コーデック不要</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>白より明るく描画</v>
+        <v>ピクセルを表示</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>profiletool 自身がデコードするためブラウザに依存しません</v>
+        <v>白より明るく描画</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>このブラウザはディスプレイの HDR ヘッドルームを報告しておらず、HDR 経路の有無のみ分かります。</v>
+        <v>profiletool 自身がデコードするためブラウザに依存しません</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>ブラウザのフラグ</v>
+        <v>このブラウザはディスプレイの HDR ヘッドルームを報告しておらず、HDR 経路の有無のみ分かります。</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>有効</v>
+        <v>ブラウザのフラグ</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>無効</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>ここでは検出できません</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>このブラウザで HDR を描画するのに必要です。WebGPU がないため、HDR キャンバスが唯一の経路です。プロファイルの検査はこれなしで動作します。</v>
+        <v>ここでは検出できません</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>任意：HDR は WebGPU で描画できますが、有効にすると HDR キャンバス経路が加わり、profiletool が画面の実際の HDR ヘッドルームを読めるようになります。</v>
+        <v>このブラウザで HDR を描画するのに必要です。WebGPU がないため、HDR キャンバスが唯一の経路です。プロファイルの検査はこれなしで動作します。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>Web ページはフラグのページを開けません。これをアドレスバーに貼り付けて Enabled にし、ブラウザを再起動してください。</v>
+        <v>任意：HDR は WebGPU で描画できますが、有効にすると HDR キャンバス経路が加わり、profiletool が画面の実際の HDR ヘッドルームを読めるようになります。</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>コピー</v>
+        <v>Web ページはフラグのページを開けません。これをアドレスバーに貼り付けて Enabled にし、ブラウザを再起動してください。</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>コピーしました</v>
+        <v>コピー</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>コピーに失敗しました — アドレスを選択してコピーしてください。</v>
+        <v>コピーしました</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>ピクセル比</v>
+        <v>コピーに失敗しました — アドレスを選択してコピーしてください。</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>現在のモニター</v>
+        <v>ピクセル比</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>名前なし</v>
+        <v>現在のモニター</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>メイン</v>
+        <v>名前なし</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>内蔵</v>
+        <v>メイン</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>HDR ヘッドルーム</v>
+        <v>内蔵</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>このブラウザでは公開されていません</v>
+        <v>HDR ヘッドルーム</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium はこれを段（stop）で報告します：ディスプレイのピーク輝度 ÷ SDR 白レベルの log₂。Windows では、Chrome がディスプレイを読み直したとき（ウィンドウを別の画面へ移動、または Chrome を再アクティブ化）にのみ更新され、明るさを変えても更新されません。</v>
+        <v>このブラウザでは公開されていません</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} 段（≈ SDR 白の {ratio} 倍）</v>
+        <v>Chromium はこれを段（stop）で報告します：ディスプレイのピーク輝度 ÷ SDR 白レベルの log₂。Windows では、Chrome がディスプレイを読み直したとき（ウィンドウを別の画面へ移動、または Chrome を再アクティブ化）にのみ更新され、明るさを変えても更新されません。</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} 段（≈ SDR 白の {ratio} 倍）</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>指定ディスプレイヘッドルームでのゲイン</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>このディスプレイで HDR 画像を 1 枚表示します。ブラウザがデコードできるファイルはブラウザ自身が表示し、OpenEXR と Radiance HDR は profiletool がデコードして描画します。</v>
+        <v>指定ディスプレイヘッドルームでのゲイン</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>HDR 画像をここにドロップするか、クリックして選択</v>
+        <v>このディスプレイで HDR 画像を 1 枚表示します。ブラウザがデコードできるファイルはブラウザ自身が表示し、OpenEXR と Radiance HDR は profiletool がデコードして描画します。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（ゲインマップ JPEG を含む）、PNG——Safari では HEIC と JPEG XL も。</v>
+        <v>HDR 画像をここにドロップするか、クリックして選択</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>別の画像を選択</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（ゲインマップ JPEG を含む）、PNG——Safari では HEIC と JPEG XL も。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>クリア</v>
+        <v>別の画像を選択</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>埋め込み ICC プロファイル</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>なし——OpenEXR は色度座標で色を表します</v>
+        <v>埋め込み ICC プロファイル</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>なし——Radiance HDR は PRIMARIES ヘッダーで色を表します</v>
+        <v>なし——OpenEXR は色度座標で色を表します</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>確認中…</v>
+        <v>なし——Radiance HDR は PRIMARIES ヘッダーで色を表します</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>なし</v>
+        <v>確認中…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>プロファイルタブで開く</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>ゲインマップ</v>
+        <v>プロファイルタブで開く</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>検出、未デコード</v>
+        <v>ゲインマップ</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>画像ではありません。プロファイルはプロファイルパネルから読み込んでください。</v>
+        <v>検出、未デコード</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>profiletool が認識できない画像形式です。</v>
+        <v>画像ではありません。プロファイルはプロファイルパネルから読み込んでください。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>TIFF のピクセルはまだここに表示されません。ブラウザは TIFF をデコードせず、16 ビット TIFF での HDR の符号化方法も未定です（フェーズ 4.3）。埋め込みプロファイルは確認できます。</v>
+        <v>profiletool が認識できない画像形式です。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>この画像はここでは表示できません：</v>
+        <v>TIFF のピクセルはまだここに表示されません。ブラウザは TIFF をデコードせず、16 ビット TIFF での HDR の符号化方法も未定です（フェーズ 4.3）。埋め込みプロファイルは確認できます。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>埋め込みプロファイルは確認できます。</v>
+        <v>この画像はここでは表示できません：</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>表示元</v>
+        <v>埋め込みプロファイルは確認できます。</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>ブラウザ</v>
+        <v>表示元</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>ブラウザ</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>HDR ディスプレイ</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>埋め込み ICC プロファイルだけで示された HDR はブラウザに無視されるため、この画像は暗く平坦に見える場合があります。</v>
+        <v>HDR ディスプレイ</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>このブラウザは画像を SDR と HDR で切り替えられないため、ブラウザの描画のまま表示します。</v>
+        <v>埋め込み ICC プロファイルだけで示された HDR はブラウザに無視されるため、この画像は暗く平坦に見える場合があります。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>ブラウザはこの画像をデコードできませんでした。</v>
+        <v>このブラウザは画像を SDR と HDR で切り替えられないため、ブラウザの描画のまま表示します。</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>出力</v>
+        <v>ブラウザはこの画像をデコードできませんでした。</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>HDR キャンバス（float16）</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU（拡張レンジ）</v>
+        <v>HDR キャンバス（float16）</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>SDR キャンバス（トーンマップ）</v>
+        <v>WebGPU（拡張レンジ）</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>サイズ</v>
+        <v>SDR キャンバス（トーンマップ）</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>最も明るいピクセル</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>SDR 白の {n} 倍</v>
+        <v>最も明るいピクセル</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>色度座標</v>
+        <v>SDR 白の {n} 倍</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>記載なし——Rec. 709 と仮定</v>
+        <v>色度座標</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from} はここでは使えません（{why}）。次の出力を使います。</v>
+        <v>記載なし——Rec. 709 と仮定</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>この出力は白より明るい値を扱えないため、トーンマップした SDR 描画を表示します。</v>
+        <v>{from} はここでは使えません（{why}）。次の出力を使います。</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>露出</v>
+        <v>この出力は白より明るい値を扱えないため、トーンマップした SDR 描画を表示します。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} 段</v>
+        <v>露出</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>デコードできません：</v>
+        <v>{n} 段</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>このファイルは {size} MB です。HDR タブで開ける画像は {max} MB までです。</v>
+        <v>デコードできません：</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>プロファイルを適用できません：</v>
+        <v>このファイルは {size} MB です。HDR タブで開ける画像は {max} MB までです。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>画像を描画できません：</v>
+        <v>プロファイルを適用できません：</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>（これらの原色は色空間を定義しません——無視し、Rec. 709 を使用）</v>
+        <v>画像を描画できません：</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>JPEG XL のプロファイルはコードストリーム内で圧縮されており、profiletool はまだ展開できません</v>
+        <v>（これらの原色は色空間を定義しません——無視し、Rec. 709 を使用）</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>デコード中…</v>
+        <v>JPEG XL のプロファイルはコードストリーム内で圧縮されており、profiletool はまだ展開できません</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>ダイナミックレンジ</v>
+        <v>デコード中…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>このブラウザは両端のみで、中間の混合はできません。</v>
+        <v>ダイナミックレンジ</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>profiletool 自身がデコードするため、ブラウザに依存しません</v>
+        <v>このブラウザは両端のみで、中間の混合はできません。</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>このブラウザはデコードできます</v>
+        <v>profiletool 自身がデコードするため、ブラウザに依存しません</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>このブラウザはデコードできません</v>
+        <v>このブラウザはデコードできます</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>HEIC の表示には Safari などの WebKit ブラウザが必要です——Chrome と Firefox は macOS を含むどのプラットフォームでも HEIC をデコードしません</v>
+        <v>このブラウザはデコードできません</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>JPEG XL の表示には Safari が必要です。他のブラウザは未対応です</v>
+        <v>HEIC の表示には Safari などの WebKit ブラウザが必要です——Chrome と Firefox は macOS を含むどのプラットフォームでも HEIC をデコードしません</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>今後のリリースに延期</v>
+        <v>JPEG XL の表示には Safari が必要です。他のブラウザは未対応です</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>このディスプレイは HDR 経路を報告しないため、HDR はトーンマップした SDR で表示されます</v>
+        <v>今後のリリースに延期</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>このブラウザには HDR キャンバス経路がありません（float16 キャンバスか WebGPU が必要）</v>
+        <v>このディスプレイは HDR 経路を報告しないため、HDR はトーンマップした SDR で表示されます</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox は HDR 画像を表示せず、ゲインマップも読みません。HDR コンテンツは SDR で表示されます</v>
+        <v>このブラウザには HDR キャンバス経路がありません（float16 キャンバスか WebGPU が必要）</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>確認にはコンテナの解析だけが必要で、コーデックは不要です</v>
+        <v>Firefox は HDR 画像を表示せず、ゲインマップも読みません。HDR コンテンツは SDR で表示されます</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>HDR ディスプレイと HDR キャンバス経路の両方が使えます</v>
+        <v>確認にはコンテナの解析だけが必要で、コーデックは不要です</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>不明な形式</v>
+        <v>HDR ディスプレイと HDR キャンバス経路の両方が使えます</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{os} 上の {browser}</v>
+        <v>不明な形式</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · HDR ディスプレイを検出</v>
+        <v>{os} 上の {browser}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · SDR ディスプレイ</v>
+        <v>{name} · HDR ディスプレイを検出</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU がトーンマッピング「{mode}」を適用したため、出力は SDR に制限されます</v>
+        <v>{name} · SDR ディスプレイ</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>このブラウザは適用した WebGPU トーンマッピングを報告しないため、HDR 出力は未確認です</v>
+        <v>WebGPU がトーンマッピング「{mode}」を適用したため、出力は SDR に制限されます</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>ディスプレイのピーク</v>
+        <v>このブラウザは適用した WebGPU トーンマッピングを報告しないため、HDR 出力は未確認です</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>SDR 白の {r} 倍（{n} 段）</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× — SDR ディスプレイ</v>
+        <v>SDR 白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>不明</v>
+        <v>1× — SDR ディスプレイ</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>このディスプレイは HDR を報告しないため、ブラウザはどちらの端でもこの画像を SDR で表示します。</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>このディスプレイは HDR を報告しないため、SDR 白より明るい部分はクリップされます。「ディスプレイに合わせる」はトーンマップした描画を表示します。</v>
+        <v>このディスプレイは HDR を報告しないため、ブラウザはどちらの端でもこの画像を SDR で表示します。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>この画像は SDR 白の {img} 倍を必要としますが、このディスプレイは {disp} 倍までしか表示できないため、明るい値はクリップされます。「ディスプレイに合わせる」はそれらをディスプレイのピークへなだらかに収めます。</v>
+        <v>このディスプレイは HDR を報告しないため、SDR 白より明るい部分はクリップされます。「ディスプレイに合わせる」はトーンマップした描画を表示します。</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>ディスプレイに合わせる</v>
+        <v>この画像は SDR 白の {img} 倍を必要としますが、このディスプレイは {disp} 倍までしか表示できないため、明るい値はクリップされます。「ディスプレイに合わせる」はそれらをディスプレイのピークへなだらかに収めます。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>画像の詳細</v>
+        <v>ディスプレイに合わせる</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>使用不可——この画像はブラウザが描画するため、指定したピークに制限できません</v>
+        <v>画像の詳細</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>使用不可——この出力は SDR 白を超える明るさを表示できません</v>
+        <v>使用不可——この画像はブラウザが描画するため、指定したピークに制限できません</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>使用不可——このディスプレイのピークは不明です</v>
+        <v>使用不可——この出力は SDR 白を超える明るさを表示できません</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>拡大</v>
+        <v>使用不可——このディスプレイのピークは不明です</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>縮小</v>
+        <v>拡大</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>画像を全体表示</v>
+        <v>縮小</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>実ピクセル（1:1）</v>
+        <v>画像を全体表示</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>ドラッグでパン · Ctrl+ホイールでズーム · ダブルクリックでリセット</v>
+        <v>実ピクセル（1:1）</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>ドラッグで画像領域のサイズを変更、ダブルクリックで既定サイズに戻します</v>
+        <v>ドラッグでパン · Ctrl+ホイールでズーム · ダブルクリックでリセット</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>画像ビュー</v>
+        <v>ドラッグで画像領域のサイズを変更、ダブルクリックで既定サイズに戻します</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
+        <v>画像ビュー</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>上限なし</v>
+        <v>このディスプレイが報告するピークで明るさを制限します。Windows ではこの値が明るさの変更に遅れることがあります。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>上限 {n} 段（{r}×）</v>
+        <v>上限なし</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>SDR 白</v>
+        <v>上限 {n} 段（{r}×）</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>SDR 白パッチ</v>
+        <v>比較用の単純な SDR 白です。HDR ディスプレイでは HDR のハイライトがこれより明るく見えます。</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
+        <v>SDR 白パッチ</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>プロファイルを割り当て</v>
+        <v>ドラッグで移動、ダブルクリックで画像の横に戻します。</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>なし——ファイル自身の指定どおり</v>
+        <v>プロファイルを割り当て</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>埋め込みプロファイル（{n} B）</v>
+        <v>なし——ファイル自身の指定どおり</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>プール内の HDR プロファイル</v>
+        <v>埋め込みプロファイル（{n} B）</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>プロファイル</v>
+        <v>プール内の HDR プロファイル</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>埋め込みプロファイル</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>カラーエンジンの経路</v>
+        <v>埋め込みプロファイル</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR 経路、ゲインカーブ適用</v>
+        <v>カラーエンジンの経路</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>HDR 経路、ゲインカーブなし</v>
+        <v>HDR 経路、ゲインカーブ適用</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>焼き込み AToB0——HDR 経路ではありません</v>
+        <v>HDR 経路、ゲインカーブなし</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>伝達関数</v>
+        <v>焼き込み AToB0——HDR 経路ではありません</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR 基準白</v>
+        <v>伝達関数</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>リニア値</v>
+        <v>HDR 基準白</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>ファイルの 1.0 = HDR 基準白</v>
+        <v>リニア値</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>ファイルの 1.0 = 1 cd/m²（ICC.1 箇条 8.10.2 a）</v>
+        <v>ファイルの 1.0 = HDR 基準白</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>OpenEXR と Radiance HDR のファイルは慣例として SDR 白を 1.0 に置きますが、ICC のリニア伝達関数は 1.0 を 1 cd/m² と解釈します。既定では、ファイルの 1.0 がプロファイルの HDR 基準白になるようにスケーリングします。</v>
+        <v>ファイルの 1.0 = 1 cd/m²（ICC.1 箇条 8.10.2 a）</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>入力スケール</v>
+        <v>OpenEXR と Radiance HDR のファイルは慣例として SDR 白を 1.0 に置きますが、ICC のリニア伝達関数は 1.0 を 1 cd/m² と解釈します。既定では、ファイルの 1.0 がプロファイルの HDR 基準白になるようにスケーリングします。</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} — ファイルの 1.0 = 基準白</v>
+        <v>入力スケール</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>なし — ファイルの 1.0 = 1 cd/m²</v>
+        <v>×{w} — ファイルの 1.0 = 基準白</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>目標ヘッドルーム</v>
+        <v>なし — ファイルの 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>基準白の {r} 倍（{n} 段）</v>
+        <v>目標ヘッドルーム</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>トーンマッピング</v>
+        <v>基準白の {r} 倍（{n} 段）</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>自動（8.10.3 項の優先順位）</v>
+        <v>トーンマッピング</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>ゲインカーブ（HAGC）</v>
+        <v>自動（8.10.3 項の優先順位）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>焼き込み SDR フォールバック（AToB0）</v>
+        <v>ゲインカーブ（HAGC）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>オフ——改訂前の CMM と同じ</v>
+        <v>焼き込み SDR フォールバック（AToB0）</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>プロファイルを適用中…</v>
+        <v>オフ——改訂前の CMM と同じ</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
+        <v>プロファイルを適用中…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
+        <v>{format} はリニア光を保持するため、伝達関数が Linear（8）のプロファイルが必要です。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
+        <v>プロファイルの割り当てには 3 チャンネル RGB 画像が必要です。</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>HDR プロファイル</v>
+        <v>値を解釈するには、上でプロファイルを割り当ててください。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>リニア伝達関数</v>
+        <v>HDR プロファイル</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>非リニア伝達関数（PQ、HLG）</v>
+        <v>リニア伝達関数</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>HDR プロファイル — リニア伝達関数</v>
+        <v>非リニア伝達関数（PQ、HLG）</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
+        <v>HDR プロファイル — リニア伝達関数</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
+        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
+        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
+        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>ベースライン</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>カラーエンジンによるプレビュー</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
+        <v>カラーエンジンによるプレビュー</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>{h} 段向けにトーンマッピング</v>
+        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
+        <v>{h} 段向けにトーンマッピング</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>基準白</v>
+        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>ディスプレイのピーク</v>
+        <v>基準白</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>プレビューを表示できません：{why}</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
+        <v>プレビューを表示できません：{why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>全ヘッドルームでのゲイン</v>
+        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
+        <v>全ヘッドルームでのゲイン</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>入力（HDR 基準白に対する段数）</v>
+        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>ディスプレイのヘッドルーム（段）</v>
+        <v>入力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>ゲイン（段）</v>
+        <v>ディスプレイのヘッドルーム（段）</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>タグ内のカーブ</v>
+        <v>ゲイン（段）</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>ベースライン</v>
+        <v>タグ内のカーブ</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>スライダー</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>入力 = ディスプレイのピーク</v>
+        <v>スライダー</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>ヘッドルーム別のグレートーンカーブ</v>
+        <v>入力 = ディスプレイのピーク</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
+        <v>ヘッドルーム別のグレートーンカーブ</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>出力（HDR 基準白に対する段数）</v>
+        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} 段</v>
+        <v>出力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} 段（ベースライン）</v>
+        <v>{h} 段</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} 段（スライダー）</v>
+        <v>{h} 段（ベースライン）</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>{h} 段（スライダー）</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>{h} 段で適用</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>変化なし</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>{h} 段での出力</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>ディスプレイを識別</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>ディスプレイイベント</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>原色</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>伝達特性</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>マトリクス係数</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>フルレンジ</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>ナローレンジ</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>レポート</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>you@example.com</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>（任意）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>登録</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>閉じる</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>エラー:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,2949 +1197,2957 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>名前で並べ替え</v>
+        <v>タップして選択し、タブをタップして送ります。</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>名前で並べ替え</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>.cube から新しいプロファイル</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加されて開かれます。「ICC プロファイルを保存」をクリックするまでダウンロードはされません。</v>
+        <v>.cube から新しいプロファイル</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>.cube ファイルを選択</v>
+        <v>Adobe/Resolve の .cube 3D LUT から ICC DeviceLink を作成します。結果はプールに追加されて開かれます。「ICC プロファイルを保存」をクリックするまでダウンロードはされません。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>.cube ファイルを選択</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>またはここにドロップするか、下に貼り付けてください</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>キャンセル</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>DeviceLink を作成</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>作成中…</v>
+        <v>DeviceLink を作成</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>プロファイル</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>比較</v>
+        <v>プロファイル</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>リンク</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>スペクトル</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>プールからこのタブにプロファイルをドラッグします</v>
+        <v>スペクトル</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>削除</v>
+        <v>プールからこのタブにプロファイルをドラッグします</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>プロファイルが選択されていません</v>
+        <v>削除</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
+        <v>プロファイルが選択されていません</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>まだ比較するものがありません</v>
+        <v>プールから「プロファイル」タブにプロファイルをドラッグして確認します。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
+        <v>まだ比較するものがありません</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>色域比較</v>
+        <v>1 つ以上のプロファイルを「比較」タブにドラッグします。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>レンダリングインテント</v>
+        <v>3D 色域と 2D スライスのビューがここに追加されます。累積：</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>シェル</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>ワイヤーフレーム</v>
+        <v>シェル</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>軸の数値</v>
+        <v>ワイヤーフレーム</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>不透明度</v>
+        <v>軸の数値</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>色</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>単色</v>
+        <v>色</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>値による</v>
+        <v>単色</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>色相による</v>
+        <v>値による</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>回転</v>
+        <v>色相による</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>ターンテーブル</v>
+        <v>回転</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>オービット</v>
+        <v>ターンテーブル</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>ドラッグ速度</v>
+        <v>オービット</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>ロール</v>
+        <v>ドラッグ速度</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>ロール速度</v>
+        <v>ロール</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>色域を構築中…</v>
+        <v>ロール速度</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>色域なし</v>
+        <v>色域を構築中…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>表示/非表示</v>
+        <v>色域なし</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D 色域シェル</v>
+        <v>表示/非表示</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D 色域スライス</v>
+        <v>3D 色域シェル</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>平面</v>
+        <v>2D 色域スライス</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>リンク</v>
+        <v>選択したプロファイルには、色域を導出できるデバイス→PCS 変換がありません。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
+        <v>リンク</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
+        <v>DeviceLink の生成と複数プロファイルの変換は後の段階で提供されます。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4 ディスプレイメーカー</v>
+        <v>さらに多くのリンクメーカー (DeviceLink, …) がここに追加されます。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
+        <v>V4 ディスプレイメーカー</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB ディスプレイ</v>
+        <v>V5 RGB ディスプレイと V5 オブザーバープロファイルをここにドラッグして、V4 ディスプレイプロファイルを作成します。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>ディスプレイプロファイルをドロップ</v>
+        <v>V5 RGB ディスプレイ</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 オブザーバー (PCC)</v>
+        <v>ディスプレイプロファイルをドロップ</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>オブザーバープロファイルをドロップ</v>
+        <v>V5 オブザーバー (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
+        <v>オブザーバープロファイルをドロップ</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>V4 ディスプレイプロファイルを作成</v>
+        <v>V5 RGB ディスプレイでもオブザーバーでもないプロファイルは無視されました。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>プロファイル名</v>
+        <v>V4 ディスプレイプロファイルを作成</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>作成</v>
+        <v>プロファイル名</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>作成中…</v>
+        <v>作成</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>リンクパイプライン</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
+        <v>リンクパイプライン</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>完了</v>
+        <v>プロファイルのチェーンを作成し、DeviceLinkの作成、画像の変換、またはカラーデータセットの変換を行います。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
+        <v>完了</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>画像を確認中…</v>
+        <v>変換する画像をドロップ（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
+        <v>画像を確認中…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
+        <v>サポートされていない画像形式です（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>画像を変換</v>
+        <v>画像が大きすぎます（{mp} MP、上限 {max} MP）。</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>変換中…</v>
+        <v>画像を変換</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>削除済み</v>
+        <v>チェーンを開始するにはプロファイルをドロップしてください</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>前に移動</v>
+        <v>削除済み</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>後に移動</v>
+        <v>前に移動</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>上に移動</v>
+        <v>後に移動</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>下に移動</v>
+        <v>上に移動</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>レンダリングインテント（すべて）</v>
+        <v>下に移動</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>この変換のレンダリングインテント</v>
+        <v>レンダリングインテント（すべて）</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
+        <v>この変換のレンダリングインテント</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
+        <v>変換ごとに異なるレンダリングインテントが使用されています</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
+        <v>チェーンの向きを反転（先頭の変換を反転し、チェーン全体に波及します）</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>チェーン</v>
+        <v>チェーン内のプロファイルがプールから削除されました — 続行するには削除してください。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>チェーンを解析できませんでした。</v>
+        <v>チェーン</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>チェーンを確認中…</v>
+        <v>チェーンを解析できませんでした。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>チェーンが接続していません（{detail}）。</v>
+        <v>チェーンを確認中…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
+        <v>チェーンが接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>画像を処理する前にチェーンを修正してください</v>
+        <v>プロファイル{n}は前の段階に接続していません（{detail}）。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>クリア</v>
+        <v>画像を処理する前にチェーンを修正してください</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>DeviceLinkを作成</v>
+        <v>クリア</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink名</v>
+        <v>DeviceLinkを作成</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>作成中…</v>
+        <v>DeviceLink名</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
+        <v>作成中…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
+        <v>「{name}」を作成しました — プールとこのタブに追加されました。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>画像を処理するにはチェーンを作成してください</v>
+        <v>{src}の画像をドロップして{dst}に変換します — 結果はダウンロードされ、保存はされません。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
+        <v>画像を処理するにはチェーンを作成してください</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>変換した画像を保存しました。</v>
+        <v>このチェーンは画像カラースペースで始まり終わっていません</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
+        <v>変換した画像を保存しました。</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>そのファイルを読み込めませんでした。</v>
+        <v>カラーデータセットをドロップ（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>データファイルが大きすぎます。</v>
+        <v>そのファイルを読み込めませんでした。</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>データを変換</v>
+        <v>データファイルが大きすぎます。</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>変換中…</v>
+        <v>データを変換</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>優先</v>
+        <v>変換中…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>観測者</v>
+        <v>優先</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>光源</v>
+        <v>観測者</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>条件</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>重複を{n}件フィルタ</v>
+        <v>条件</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>中央値</v>
+        <v>重複を{n}件フィルタ</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>平均値</v>
+        <v>中央値</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>パッチ</v>
+        <v>平均値</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>重複{n}件</v>
+        <v>パッチ</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>変換結果</v>
+        <v>重複{n}件</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} ・ {n}パッチ</v>
+        <v>変換結果</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
+        <v>{src} → {dst} ・ {n}パッチ</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>名前を付けて保存</v>
+        <v>{total}件中最初の{shown}件を表示中 — 保存するとすべて書き出されます。</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>保存</v>
+        <v>名前を付けて保存</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>変換を反転</v>
+        <v>保存</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>反転中…</v>
+        <v>変換を反転</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>反転</v>
+        <v>反転中…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>最後の段階</v>
+        <v>反転</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>最初の段階</v>
+        <v>最後の段階</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>{in}のデータ → {out}を検索</v>
+        <v>最初の段階</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
+        <v>{in}のデータ → {out}を検索</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
+        <v>反転には2〜3個のプロファイルからなるチェーンが必要です</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔEコスト</v>
+        <v>データセットは{in}である必要があります。逆検索により{out}とパッチごとの可逆性コストが得られます。</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>この画像には埋め込みICCプロファイルがあります。</v>
+        <v>ΔEコスト</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>抽出してチェーンに追加</v>
+        <v>この画像には埋め込みICCプロファイルがあります。</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>抽出中…</v>
+        <v>抽出してチェーンに追加</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>閉じる</v>
+        <v>抽出中…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>画像出力オプション</v>
+        <v>埋め込みプロファイルを抽出しました — プールに追加し、チェーンの先頭に配置しました。</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>エンコーディング</v>
+        <v>画像出力オプション</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>元と同じ</v>
+        <v>エンコーディング</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8ビット</v>
+        <v>元と同じ</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16ビット</v>
+        <v>8ビット</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>浮動小数点（32ビット）</v>
+        <v>16ビット</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>圧縮</v>
+        <v>浮動小数点（32ビット）</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>なし</v>
+        <v>圧縮</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>プレーナー</v>
+        <v>なし</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>コンポジット</v>
+        <v>プレーナー</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>セパレート</v>
+        <v>コンポジット</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM補間</v>
+        <v>セパレート</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>四面体</v>
+        <v>CMM補間</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>線形</v>
+        <v>四面体</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>ICCを埋め込む</v>
+        <v>線形</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
+        <v>ICCを埋め込む</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>スペクトルTIFFを組み立て</v>
+        <v>エンコーディング、圧縮、プレーナー形式は保存されるTIFFに反映されます。RGB/Gray出力は、TIFF専用のオプション（浮動小数点、LZW/ZIP、セパレート）が設定されない限りPNGのままです。</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
+        <v>スペクトルTIFFを組み立て</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
+        <v>単一チャンネルのスペクトル画像をチャンネル順にドロップすると、1つのマルチチャンネルTIFFに組み立てられます。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>ch</v>
+        <v>スペクトル画像をここにドロップ（またはクリックして選択）</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>組み立てて保存</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>組み立て中…</v>
+        <v>組み立てて保存</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n}チャンネルを組み立てました。</v>
+        <v>組み立て中…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
+        <v>{n}チャンネルを組み立てました。</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>キャンセル</v>
+        <v>画像として認識できるものがありません（TIFF、PNGまたはJPEG）。</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} 件のファイルが読み込まれませんでした</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
+        <v>{n} 件のファイルが読み込まれませんでした</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>これらのファイルは ICC プロファイルではないため、プールに追加されませんでした：</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>ここに ICC プロファイルをドロップ</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>または</v>
+        <v>ここに ICC プロファイルをドロップ</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>ファイルを選択</v>
+        <v>または</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc および .icm ファイル</v>
+        <v>ファイルを選択</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>ヘッダー</v>
+        <v>.icc および .icm ファイル</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>タグ</v>
+        <v>ヘッダー</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>検証</v>
+        <v>タグ</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>分析</v>
+        <v>検証</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>中立軸インキング</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
+        <v>中立軸インキング</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>明度が白（L*=100）から黒（L*=0）へ変化する際に、中立軸（a*=b*=0）に沿って付与されるデバイス色材。</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
+        <v>中立軸インキングは出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>レンダリングインテント</v>
+        <v>このプロファイルにはサンプリングする B2A（PCS→デバイス）テーブルがありません。</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% インキ</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* 出力（トーン）</v>
+        <v>% インキ</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 出力（トーン）</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>極値の測色</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>プロファイルの再現範囲の両端：基材の白、印刷できる最も暗い黒、その黒に要するインキ量、そして各色相が最も鮮やかになる点。</v>
+        <v>極値の測色</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>白色点は色材ゼロのときの色——すなわち素の基材です。黒色点は、PCS の黒（L*=0、a*=b*=0）を選択した B2A テーブルに通してプロファイルが黒に対して選ぶインキングを求め、そのインキングを A2B1 で読み戻して得られます。総インキ量（TAC）はそのインキングの合計です。絶対測色は基材そのものの色を示し、相対測色はそれを完全な白に基準化し直します。</v>
+        <v>プロファイルの再現範囲の両端：基材の白、印刷できる最も暗い黒、その黒に要するインキ量、そして各色相が最も鮮やかになる点。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>相対</v>
+        <v>白色点は色材ゼロのときの色——すなわち素の基材です。黒色点は、PCS の黒（L*=0、a*=b*=0）を選択した B2A テーブルに通してプロファイルが黒に対して選ぶインキングを求め、そのインキングを A2B1 で読み戻して得られます。総インキ量（TAC）はそのインキングの合計です。絶対測色は基材そのものの色を示し、相対測色はそれを完全な白に基準化し直します。</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>絶対</v>
+        <v>相対</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>白色点</v>
+        <v>絶対</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>黒色点</v>
+        <v>白色点</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>黒色点でのインキング</v>
+        <v>黒色点</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>黒色点でのインキング</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>このプロファイルにはメディア白色点タグがないため、絶対測色は利用できません。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>極値の測色は出力（プリンター）プロファイルでのみ利用できます——色材ゼロが素の基材であることを前提とします。</v>
+        <v>このプロファイルにはメディア白色点タグがないため、絶対測色は利用できません。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>ベタとクロマ最大点</v>
+        <v>極値の測色は出力（プリンター）プロファイルでのみ利用できます——色材ゼロが素の基材であることを前提とします。</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>各インキ頂点の位置と、そこに至る途中で最もクロマが高くなる点です。A2B1 を通して測るため、これらの行は上のレンダリングインテントでは変化しません。素性のよいプロファイルでは 2 つの行が一致します。クロマ最大点がベタより手前に来る場合、その先のインキは暗くしているだけです。</v>
+        <v>ベタとクロマ最大点</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>色相</v>
+        <v>各インキ頂点の位置と、そこに至る途中で最もクロマが高くなる点です。A2B1 を通して測るため、これらの行は上のレンダリングインテントでは変化しません。素性のよいプロファイルでは 2 つの行が一致します。クロマ最大点がベタより手前に来る場合、その先のインキは暗くしているだけです。</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>ベタ</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* 最大</v>
+        <v>ベタ</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>そのインキング</v>
+        <v>C* 最大</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>クロマ最大点がベタより手前で到達しています——この点より先のインキは暗くするだけです。</v>
+        <v>そのインキング</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>シャドウ部のインキ使用量</v>
+        <v>クロマ最大点がベタより手前で到達しています——この点より先のインキは暗くするだけです。</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>意図的に暗い一定の明度で a*b* 平面を横切る 4 本の直線経路を、選択した B2A テーブルに通します。すべてのサンプルが同じ L* を共有するため、ある色材に現れる急な段差や反転は色相とクロマの扱いのみに由来します——シャドウ部の色域マッピングアーティファクトの兆候です。</v>
+        <v>シャドウ部のインキ使用量</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>シャドウ部のインキ使用量は出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>意図的に暗い一定の明度で a*b* 平面を横切る 4 本の直線経路を、選択した B2A テーブルに通します。すべてのサンプルが同じ L* を共有するため、ある色材に現れる急な段差や反転は色相とクロマの扱いのみに由来します——シャドウ部の色域マッピングアーティファクトの兆候です。</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>L* 一定の平面</v>
+        <v>シャドウ部のインキ使用量は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>黒色点補償の起点</v>
+        <v>L* 一定の平面</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>経路上の位置</v>
+        <v>黒色点補償の起点</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>経路</v>
+        <v>経路上の位置</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>中性軸を通る一次色インキ経路</v>
+        <v>経路</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>色域内の3本の経路——シアン→レッド、マゼンタ→グリーン、イエロー→ブルー——それぞれが両端の明度の中点で中性軸を通り、選択した B2A テーブルを通ります。すべてのサンプルが色域内にあるため、シャドウ経路とは異なり、ある色材の急な段差や反転は色域マッピングのアーティファクトではなく CLUT の滑らかさの欠陥を示します。</v>
+        <v>中性軸を通る一次色インキ経路</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>一次色インキ経路は出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>色域内の3本の経路——シアン→レッド、マゼンタ→グリーン、イエロー→ブルー——それぞれが両端の明度の中点で中性軸を通り、選択した B2A テーブルを通ります。すべてのサンプルが色域内にあるため、シャドウ経路とは異なり、ある色材の急な段差や反転は色域マッピングのアーティファクトではなく CLUT の滑らかさの欠陥を示します。</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>経路上の位置（中点が中性）</v>
+        <v>一次色インキ経路は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>このインテントに黒点補償を適用しました。</v>
+        <v>経路上の位置（中点が中性）</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>インキ使用量の統計</v>
+        <v>このインテントに黒点補償を適用しました。</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>プロファイルが各色材をどれだけ使用するかを、合計と全体に対する割合で示します——分版のインキ消費の特徴です。</v>
+        <v>インキ使用量の統計</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>インキ使用量の統計は出力（プリンター）プロファイルでのみ利用できます。</v>
+        <v>プロファイルが各色材をどれだけ使用するかを、合計と全体に対する割合で示します——分版のインキ消費の特徴です。</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>中性軸</v>
+        <v>インキ使用量の統計は出力（プリンター）プロファイルでのみ利用できます。</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>平均被覆率</v>
+        <v>中性軸</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>インキの割合</v>
+        <v>平均被覆率</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>インキの割合は中性構築の指紋です——各色材が使用インキ総量に占める割合で、サンプル数に依存しません。</v>
+        <v>インキの割合</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>色域内の点</v>
+        <v>インキの割合は中性構築の指紋です——各色材が使用インキ総量に占める割合で、サンプル数に依存しません。</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>色域内のすべての色に対するインキ使用量には B2A 方向の色域境界が必要ですが、まだ構築されていません——保留中です。</v>
+        <v>色域内の点</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>要約する色材データがありません。</v>
+        <v>色域内のすべての色に対するインキ使用量には B2A 方向の色域境界が必要ですが、まだ構築されていません——保留中です。</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>下で B2A（PCS→デバイス）テーブルを選択すると、各色材のグレースケールのインキ被覆画像も表示されます。</v>
+        <v>要約する色材データがありません。</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>同じ格子上での各色材のインキ被覆（暗いほどインキが多い）。</v>
+        <v>下で B2A（PCS→デバイス）テーブルを選択すると、各色材のグレースケールのインキ被覆画像も表示されます。</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>シアン</v>
+        <v>同じ格子上での各色材のインキ被覆（暗いほどインキが多い）。</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>マゼンタ</v>
+        <v>シアン</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>イエロー</v>
+        <v>マゼンタ</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>レッド</v>
+        <v>イエロー</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>グリーン</v>
+        <v>レッド</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>ブルー</v>
+        <v>グリーン</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>ブラック</v>
+        <v>ブルー</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>知覚的</v>
+        <v>ブラック</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>相対比色</v>
+        <v>知覚的</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>彩度</v>
+        <v>相対比色</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>絶対比色</v>
+        <v>彩度</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>プロファイル統計</v>
+        <v>絶対比色</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
+        <v>プロファイル統計</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
+        <v>レンダリングインテントごとのプロファイル全体の指標：デバイス→PCS 変換が囲む色域体積（ΔE*ab³）と、B2A ラウンドトリップ精度——プロファイルを通した Lab → デバイス → Lab 往復の ΔE*ab。</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>レンダリングインテント</v>
+        <v>このプロファイルにはデバイス↔PCS CLUT がありません——プロファイル統計は適用されません（例：マトリクス/TRC ディスプレイプロファイル）。</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>色域体積 (ΔE³)</v>
+        <v>レンダリングインテント</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>往復 ΔE</v>
+        <v>色域体積 (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
+        <v>往復 ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>平均</v>
+        <v>この色域の境界が崩壊したか、ほとんど未定義のため、この色域体積は信頼できません。</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>分析中…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>分析</v>
+        <v>分析中…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>プロット</v>
+        <v>デバイス→PCS 変換から導くプロファイル全体の品質分析。</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>生出力</v>
+        <v>プロット</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>生出力</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>カーブ</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>入力カーブ</v>
+        <v>カーブ</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>出力カーブ</v>
+        <v>入力カーブ</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT 画像</v>
+        <v>出力カーブ</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>色域画像</v>
+        <v>CLUT 画像</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>色度</v>
+        <v>色域画像</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>散布図</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>トーンレスポンスカーブ</v>
+        <v>散布図</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>カーブ表</v>
+        <v>トーンレスポンスカーブ</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>テーブル</v>
+        <v>カーブ表</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>データ</v>
+        <v>テーブル</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>評価</v>
+        <v>データ</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>読み込み中…</v>
+        <v>評価</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>入力</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>出力</v>
+        <v>入力</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>浮動小数点</v>
+        <v>出力</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>グリッド点</v>
+        <v>浮動小数点</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>正規化</v>
+        <v>グリッド点</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>人間可読</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>デバイス → PCS</v>
+        <v>人間可読</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → デバイス</v>
+        <v>デバイス → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>CLUT グリッドなし</v>
+        <v>PCS → デバイス</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>読み込み中…</v>
+        <v>CLUT グリッドなし</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
+        <v>読み込み中…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>無効なプロファイル URL:</v>
+        <v>ニュートラル = 色域内 · 赤 = 色域外</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>プロファイルを取得できませんでした:</v>
+        <v>無効なプロファイル URL:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
+        <v>プロファイルを取得できませんでした:</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Profile Assessment WG レポートを読み込み中…</v>
+        <v>この外部サイトから ICC プロファイルを読み込みますか？</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Profile Assessment WG チェックを実行中…</v>
+        <v>Profile Assessment WG レポートを読み込み中…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG レポート</v>
+        <v>Profile Assessment WG チェックを実行中…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>セキュリティ</v>
+        <v>Profile Assessment WG レポート</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>適合性</v>
+        <v>セキュリティ</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>品質</v>
+        <v>適合性</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>レポート</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>you@example.com</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>（任意）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>登録</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>閉じる</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>エラー:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ja.xlsx
+++ b/translations/Eng-Ja.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3475,26 +3475,26 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>チェーンに HDR プロファイル</v>
+        <v>チェーンに HDR ColorSpace プロファイル</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>HDR プロファイルを通す変換はその AToB0Tag（8.10.6 が要求する焼き込み済み SDR レンダリング）を使います。8.10.1 が TRC タグを許さないためです。結果はそのフォールバックであり、HDR の挙動ではありません。</v>
+        <v>HDR プロファイルを通す変換はその AToB0Tag（8.7.1.5 が要求する焼き込み済み SDR レンダリング）を使います。ColorSpace プロファイルは TRC タグを持たないためです。結果はそのフォールバックであり、HDR の挙動ではありません。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>これらは TRC タグを持たない HDR プロファイルのため、色域は AToB0Tag から構築されます。これは HDR 処理を行わないコンシューマ向けに 8.10.6 が要求する焼き込み済み SDR レンダリングです。プロファイルの HDR 色域ではなく、それは有界の PCS には描けません。</v>
+        <v>これらは TRC タグを持たない HDR プロファイルのため、色域は AToB0Tag から構築されます。これは HDR 処理を行わないコンシューマ向けに 8.7.1.5 が要求する焼き込み済み SDR レンダリングです。プロファイルの HDR 色域ではなく、それは有界の PCS には描けません。</v>
       </c>
     </row>
     <row r="387">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>ファイルの 1.0 = 1 cd/m²（ICC.1 箇条 8.10.2 a）</v>
+        <v>ファイルの 1.0 = 1 cd/m²（ICC.1 箇条 8.7.1.2 a）</v>
       </c>
     </row>
     <row r="532">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>自動（8.10.3 項の優先順位）</v>
+        <v>自動（8.7.1.3 項の優先順位）</v>
       </c>
     </row>
     <row r="540">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>HDR プロファイル</v>
+        <v>HDR ColorSpace プロファイル</v>
       </c>
     </row>
     <row r="548">
@@ -4803,1263 +4803,1271 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR プロファイル — リニア伝達関数</v>
+        <v>HDR ColorSpace プロファイル — リニア伝達関数</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>HDR プロファイル — PQ / HLG 伝達関数</v>
+        <v>HDR ColorSpace プロファイル — PQ / HLG 伝達関数</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR プロファイルだけを割り当てられます。</v>
+        <v>{format} はリニア光を保持するため、伝達関数がリニアの HDR ColorSpace プロファイルだけを割り当てられます。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>プール内の PQ/HLG HDR プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR プロファイル › 非リニア伝達関数」にあります。</v>
+        <v>プール内の PQ/HLG HDR ColorSpace プロファイル {n} 件は選択肢に出ていません——プロファイルパネルの「HDR ColorSpace プロファイル › 非リニア伝達関数」にあります。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>プールにはまだリニア伝達関数の HDR プロファイルがありません。プロファイルパネルは HDR プロファイルを伝達関数ごとにまとめています。</v>
+        <v>プールにはまだリニア伝達関数の HDR ColorSpace プロファイルがありません。プロファイルパネルは HDR ColorSpace プロファイルを伝達関数ごとにまとめています。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.10.3 項）。</v>
+        <v>原色が未指定：このビルドでは HDR パスなし</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>ディスプレイヘッドルーム</v>
+        <v>IccProfLib はこのゲインカーブの適用を拒否しました：{why}。CMM は次のトーンマッピング記述子に切り替えます（8.7.1.3 項）。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} 段（≈ 基準白の {r} 倍）</v>
+        <v>ディスプレイヘッドルーム</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>ベースライン</v>
+        <v>{n} 段（≈ 基準白の {r} 倍）</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>カラーエンジンによるプレビュー</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
+        <v>カラーエンジンによるプレビュー</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>{h} 段向けにトーンマッピング</v>
+        <v>作成時のまま（ベースライン {h} 段、ゲインなし）</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
+        <v>{h} 段向けにトーンマッピング</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>基準白</v>
+        <v>同じテストピクセル（{transfer} 信号が左から右へ増加：グレー、続いて R、G、B、Y、C、M）を IccProfLib の HDR 変換に通したものです。両方の帯は HDR 基準白の {r} 倍に制限され、{h} 段のヘッドルームを持つディスプレイでの見え方になります。上の帯が平坦にクリップする箇所では、ゲインカーブがハイライトをなだらかに抑えます。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>ディスプレイのピーク</v>
+        <v>基準白</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>プレビューを表示できません：{why}</v>
+        <v>ディスプレイのピーク</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
+        <v>プレビューを表示できません：{why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>全ヘッドルームでのゲイン</v>
+        <v>このプロファイルではカラーエンジンが HDR パスを使いませんでした</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
+        <v>全ヘッドルームでのゲイン</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>入力（HDR 基準白に対する段数）</v>
+        <v>各ディスプレイヘッドルームでグレー入力にかかるゲイン：青は圧縮、赤は伸張、白は変化なし。点線はタグ内のカーブ、実線はベースライン、琥珀色の線はスライダー、破線の対角線は入力がディスプレイのピークに達する位置です。クリックでスライダーを移動します。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>ディスプレイのヘッドルーム（段）</v>
+        <v>入力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>ゲイン（段）</v>
+        <v>ディスプレイのヘッドルーム（段）</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>タグ内のカーブ</v>
+        <v>ゲイン（段）</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>ベースライン</v>
+        <v>タグ内のカーブ</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>スライダー</v>
+        <v>ベースライン</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>入力 = ディスプレイのピーク</v>
+        <v>スライダー</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>ヘッドルーム別のグレートーンカーブ</v>
+        <v>入力 = ディスプレイのピーク</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
+        <v>ヘッドルーム別のグレートーンカーブ</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>出力（HDR 基準白に対する段数）</v>
+        <v>タグに格納された各ヘッドルームでのグレートーンカーブを、低（青）から高（赤）へ色分けし、スライダーのカーブを琥珀色で示します。両軸とも段数なので、対角線は変化なしを表します。</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} 段</v>
+        <v>出力（HDR 基準白に対する段数）</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} 段（ベースライン）</v>
+        <v>{h} 段</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>{h} 段（スライダー）</v>
+        <v>{h} 段（ベースライン）</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
+        <v>{h} 段（スライダー）</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
+        <v>タグ内のカーブ（ヘッドルーム順）：{list} 段。ベースライン {b} 段、HDR 基準白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
+        <v>このヘッドルームはタグ内のカーブの範囲外のため、最も近いカーブをそのまま使います——ライブラリは範囲外へ外挿しません。</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
+        <v>一部の傾きはタグに格納されておらず、導出値（PCHIP）です。この導出は SMPTE の条項を再構成したものなので、それらのカーブ形状は暫定と考えてください。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
+        <v>このタグは基準白に対するトーンマッピングを要求するため、カーブはファイルから読むのではなくライブラリが構成します（委員会草案の構成）。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
+        <v>代替画像なし：このタグはトーンマッピングを求めず、ディスプレイの色域ボリュームへのクランプだけを求めます。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>{h} 段のカーブ（ゲインなし）</v>
+        <v>このヘッドルームで混合される 2 本のカーブは色チャンネルの混合方法が異なるため、単一のゲインカーブは描けません。下のトーンカーブは正確です。</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>{h} 段のカーブ</v>
+        <v>{h} 段のカーブ（ゲインなし）</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>{h} 段で適用</v>
+        <v>{h} 段のカーブ</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>このヘッドルームで適用されるゲイン</v>
+        <v>{h} 段で適用</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
+        <v>このヘッドルームで適用されるゲイン</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>ゲイン（log2 段）</v>
+        <v>混合入力（リニア、1.0 = HDR 基準白）</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>このヘッドルームでのグレーのトーンカーブ</v>
+        <v>ゲイン（log2 段）</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>入力（× HDR 基準白）</v>
+        <v>このヘッドルームでのグレーのトーンカーブ</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>出力（× HDR 基準白）</v>
+        <v>入力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>変化なし</v>
+        <v>出力（× HDR 基準白）</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>{h} 段でのディスプレイピーク</v>
+        <v>変化なし</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>{h} 段での出力</v>
+        <v>{h} 段でのディスプレイピーク</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
+        <v>{h} 段での出力</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>ディスプレイを識別</v>
+        <v>HDR・色域・ピクセル比は、それらが異なる画面へウィンドウを移すと更新されます。</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
+        <v>ディスプレイを識別</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>このウィンドウがあるモニターを追跡中です。</v>
+        <v>このウィンドウがどのモニターにあるかを知るための許可を求めます。似た画面間でも更新され、ブラウザが公開していれば HDR ヘッドルームも表示します。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
+        <v>このウィンドウがあるモニターを追跡中です。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
+        <v>ディスプレイ識別の許可が拒否されました。このサイトの設定で変更できます。</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>ディスプレイを識別できませんでした。</v>
+        <v>このブラウザはディスプレイを識別できません。上記の自動更新のみ有効です。</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>ディスプレイイベント</v>
+        <v>ディスプレイを識別できませんでした。</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
+        <v>ディスプレイイベント</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>原色</v>
+        <v>まだイベントはありません。ウィンドウを別のモニターへドラッグしてください。</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>伝達特性</v>
+        <v>原色</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>マトリクス係数</v>
+        <v>伝達特性</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>ビデオフルレンジフラグ</v>
+        <v>マトリクス係数</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>フルレンジ</v>
+        <v>ビデオフルレンジフラグ</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>ナローレンジ</v>
+        <v>フルレンジ</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>ITU-T H.273 で未割り当て</v>
+        <v>ナローレンジ</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
+        <v>ITU-T H.273 で未割り当て</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
+        <v>原色 2（未指定）は原色をプロファイル自体に委ねます。原色はこのタグではなく着色剤タグから取得されます。</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>レポート</v>
+        <v>このタグの 4 つの予約バイトがすべてゼロではありません。</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>不合格</v>
+        <v>レポート</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>件のチェック</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
+        <v>件のチェック</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC プロファイルツール · IccProfLib 採用</v>
+        <v>iccPawgReport (iccDEV) により生成 · ICC Profile Assessment Working Group チェックリスト。</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>ICC プロファイルツール</v>
+        <v>ICC プロファイルツール · IccProfLib 採用</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>{lib} 採用</v>
+        <v>ICC プロファイルツール</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>通知を受け取る</v>
+        <v>{lib} 採用</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>profiletool の新リリース通知を受け取る</v>
+        <v>通知を受け取る</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>新しいリリースの通知を受け取る</v>
+        <v>profiletool の新リリース通知を受け取る</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>閉じる</v>
+        <v>新しいリリースの通知を受け取る</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>メールアドレス</v>
+        <v>profiletool のメジャーまたはマイナーリリース時にメールでお知らせします。パッチリリースは対象外です。アドレスは追加前に手動で確認します。</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>you@example.com</v>
+        <v>メールアドレス</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>profiletool をどのように使いますか？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>（任意）</v>
+        <v>profiletool をどのように使いますか？</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>例：印刷校正のためのICCプロファイル評価</v>
+        <v>（任意）</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
+        <v>例：印刷校正のためのICCプロファイル評価</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>キャンセル</v>
+        <v>profiletool のリリースに関するメールの受信に同意します。いつでも配信解除できます。</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>登録</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>ありがとうございます — ご連絡します。</v>
+        <v>登録</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
+        <v>ありがとうございます — ご連絡します。</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>閉じる</v>
+        <v>承認後、ウェルカムメールをお送りします。その後は profiletool の新リリース時のみご連絡します。</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>プライバシーに関する通知</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>有効なメールアドレスを入力してください。</v>
+        <v>プライバシーに関する通知</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
+        <v>有効なメールアドレスを入力してください。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>フォームを確認してもう一度お試しください。</v>
+        <v>リクエストが多すぎます。しばらくしてからもう一度お試しください。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
+        <v>フォームを確認してもう一度お試しください。</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>ネットワークエラーです。もう一度お試しください。</v>
+        <v>リクエストを送信できませんでした。もう一度お試しください。</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>エラー:</v>
+        <v>ネットワークエラーです。もう一度お試しください。</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>XML に変換</v>
+        <v>エラー:</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>JSON に変換</v>
+        <v>XML に変換</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>ICC に変換</v>
+        <v>JSON に変換</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>XML に変換中…</v>
+        <v>ICC に変換</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>JSON に変換中…</v>
+        <v>XML に変換中…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>ICC に変換中…</v>
+        <v>JSON に変換中…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>ICC プロファイルを読み込み</v>
+        <v>ICC に変換中…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
+        <v>ICC プロファイルを読み込み</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>プロファイル ID</v>
+        <v>ICC プロファイル ファイルのドロップ ゾーン</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>タグが見つかりません。</v>
+        <v>プロファイル ID</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>タグ名</v>
+        <v>タグが見つかりません。</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>タグ名</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>オフセット</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>サイズ</v>
+        <v>オフセット</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>パディング</v>
+        <v>サイズ</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>読み込み後にバイトが変更されました</v>
+        <v>パディング</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>型</v>
+        <v>読み込み後にバイトが変更されました</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>{type} の配列</v>
+        <v>型</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>（内容なし）</v>
+        <v>{type} の配列</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>バイト</v>
+        <v>（内容なし）</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>完全な説明を読み込み中…</v>
+        <v>バイト</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>完全な説明を読み込めませんでした:</v>
+        <v>完全な説明を読み込み中…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
+        <v>完全な説明を読み込めませんでした:</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
+        <v>このプロファイルは完全に解析できず、適用してはなりません。以下のヘッダーとタグディレクトリは検査用にのみ表示されています。</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>検証出力なし</v>
+        <v>タグの内容を利用できません — プロファイルを完全に解析できませんでした。</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>プロファイルは有効です</v>
+        <v>検証出力なし</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>プロファイルに警告があります</v>
+        <v>プロファイルは有効です</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>プロファイルは仕様に準拠していません</v>
+        <v>プロファイルに警告があります</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>重大な検証エラー</v>
+        <v>プロファイルは仕様に準拠していません</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>不明な検証ステータス</v>
+        <v>重大な検証エラー</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>重大 — 検査用にのみ表示</v>
+        <v>不明な検証ステータス</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>警告またはエラーは見つかりませんでした。</v>
+        <v>重大 — 検査用にのみ表示</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>有効</v>
+        <v>警告またはエラーは見つかりませんでした。</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>警告</v>
+        <v>有効</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>エラー</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>不明</v>
+        <v>エラー</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>合格</v>
+        <v>不明</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>不合格</v>
+        <v>合格</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>コンテキストで表示</v>
+        <v>不合格</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>検証の詳細</v>
+        <v>コンテキストで表示</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>トリガー項目</v>
+        <v>検証の詳細</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>項目</v>
+        <v>トリガー項目</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>現在の値</v>
+        <v>項目</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>必須: 0</v>
+        <v>現在の値</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>期待値: {value}</v>
+        <v>必須: 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>無効</v>
+        <v>期待値: {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>この結果を特定の項目に関連付けられませんでした。</v>
+        <v>無効</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>閉じる</v>
+        <v>この結果を特定の項目に関連付けられませんでした。</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>XML エディタを読み込み中…</v>
+        <v>閉じる</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>JSON エディタを読み込み中…</v>
+        <v>XML エディタを読み込み中…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>JSON エディタを読み込み中…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
+        <v>未保存の XML 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● 未保存の XML 編集</v>
+        <v>未保存の JSON 編集があります。ICC プロファイルからの新しい変換で上書きしますか？</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● 未保存の JSON 編集</v>
+        <v>● 未保存の XML 編集</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
+        <v>● 未保存の JSON 編集</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
+        <v>&lt;em&gt;XML に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な XML 表現を生成します。XML は、上流の &lt;code&gt;IccToXml&lt;/code&gt; ツールと同じ IccLibXML コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>インデント</v>
+        <v>&lt;em&gt;JSON に変換&lt;/em&gt; をクリックして、このプロファイルの編集可能な JSON 表現を生成します。JSON は、上流の &lt;code&gt;IccToJson&lt;/code&gt; ツールと同じ IccLibJSON コードパスによって生成されます。</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>キーをソート</v>
+        <v>インデント</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>キーをソート</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>編集からプロファイルを書き出しましたが、再検証に失敗しました:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B707"/>
   </ignoredErrors>
 </worksheet>
 </file>